--- a/asset_import_etax.xlsx
+++ b/asset_import_etax.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N249"/>
+  <dimension ref="A1:P249"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -409,11 +409,13 @@
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="30.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="35.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="30.83203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="16" max="16" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,18 +447,24 @@
         <v>อายุการใช้งาน(เดือน)</v>
       </c>
       <c r="J1" t="str">
+        <v>ค่าเสื่อมสะสมยกมา</v>
+      </c>
+      <c r="K1" t="str">
+        <v>มูลค่าสุทธิ</v>
+      </c>
+      <c r="L1" t="str">
         <v>สถานที่</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>แผนก</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>ผู้จำหน่าย</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>เลขที่ใบแจ้งหนี้</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>หมายเหตุ</v>
       </c>
     </row>
@@ -488,20 +496,26 @@
       <c r="I2">
         <v>36</v>
       </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
+      <c r="J2">
+        <v>37288.72</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
         <v>EXP20110002</v>
       </c>
-      <c r="N2" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -532,20 +546,26 @@
       <c r="I3">
         <v>36</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
+      <c r="J3">
+        <v>10924.23</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
       </c>
       <c r="L3" t="str">
         <v/>
       </c>
       <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
         <v>EXP20110001</v>
       </c>
-      <c r="N3" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -576,20 +596,26 @@
       <c r="I4">
         <v>36</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
+      <c r="J4">
+        <v>28374.77</v>
+      </c>
+      <c r="K4">
+        <v>587.85</v>
       </c>
       <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M4" t="str">
+      <c r="O4" t="str">
         <v>EXP21020002</v>
       </c>
-      <c r="N4" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -620,20 +646,26 @@
       <c r="I5">
         <v>60</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
+      <c r="J5">
+        <v>5259.35</v>
+      </c>
+      <c r="K5">
+        <v>640.65</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
         <v>EXP2107180001</v>
       </c>
-      <c r="N5" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -664,20 +696,26 @@
       <c r="I6">
         <v>60</v>
       </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
+      <c r="J6">
+        <v>9766.35</v>
+      </c>
+      <c r="K6">
+        <v>327.1</v>
       </c>
       <c r="L6" t="str">
         <v/>
       </c>
       <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
         <v>EXP21030001</v>
       </c>
-      <c r="N6" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -708,20 +746,26 @@
       <c r="I7">
         <v>36</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
+      <c r="J7">
+        <v>6416.55</v>
+      </c>
+      <c r="K7">
+        <v>554.48</v>
       </c>
       <c r="L7" t="str">
         <v/>
       </c>
       <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
         <v>EXP2105260004</v>
       </c>
-      <c r="N7" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -752,20 +796,26 @@
       <c r="I8">
         <v>60</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
+      <c r="J8">
+        <v>17688.41</v>
+      </c>
+      <c r="K8">
+        <v>1561.12</v>
       </c>
       <c r="L8" t="str">
         <v/>
       </c>
       <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
         <v>EXP2105290001</v>
       </c>
-      <c r="N8" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -796,20 +846,26 @@
       <c r="I9">
         <v>60</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
+      <c r="J9">
+        <v>11586.07</v>
+      </c>
+      <c r="K9">
+        <v>2028.93</v>
       </c>
       <c r="L9" t="str">
         <v/>
       </c>
       <c r="M9" t="str">
+        <v/>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
         <v>EXP2109300001</v>
       </c>
-      <c r="N9" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -840,20 +896,26 @@
       <c r="I10">
         <v>60</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
+      <c r="J10">
+        <v>2680.48</v>
+      </c>
+      <c r="K10">
+        <v>470.17</v>
       </c>
       <c r="L10" t="str">
         <v/>
       </c>
       <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
         <v>EXP2109300002</v>
       </c>
-      <c r="N10" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -884,20 +946,26 @@
       <c r="I11">
         <v>36</v>
       </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
+      <c r="J11">
+        <v>3627.77</v>
+      </c>
+      <c r="K11">
+        <v>568.49</v>
       </c>
       <c r="L11" t="str">
         <v/>
       </c>
       <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
         <v>EXP2109050002</v>
       </c>
-      <c r="N11" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -928,20 +996,26 @@
       <c r="I12">
         <v>60</v>
       </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
+      <c r="J12">
+        <v>11231.31</v>
+      </c>
+      <c r="K12">
+        <v>2226.63</v>
       </c>
       <c r="L12" t="str">
         <v/>
       </c>
       <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
         <v>EXP2110300001</v>
       </c>
-      <c r="N12" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -972,20 +1046,26 @@
       <c r="I13">
         <v>60</v>
       </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
+      <c r="J13">
+        <v>7261.01</v>
+      </c>
+      <c r="K13">
+        <v>1839.92</v>
       </c>
       <c r="L13" t="str">
         <v/>
       </c>
       <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
         <v>EXP2201050002</v>
       </c>
-      <c r="N13" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1016,11 +1096,11 @@
       <c r="I14">
         <v>36</v>
       </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
+      <c r="J14">
+        <v>16251.25</v>
+      </c>
+      <c r="K14">
+        <v>4300.15</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1029,7 +1109,13 @@
         <v/>
       </c>
       <c r="N14" t="str">
-        <v>บัญชีเดิม:1705000</v>
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1060,20 +1146,26 @@
       <c r="I15">
         <v>36</v>
       </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
+      <c r="J15">
+        <v>3479.28</v>
+      </c>
+      <c r="K15">
+        <v>970.72</v>
       </c>
       <c r="L15" t="str">
         <v/>
       </c>
       <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
         <v>EXP2202030002</v>
       </c>
-      <c r="N15" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1104,20 +1196,26 @@
       <c r="I16">
         <v>36</v>
       </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
+      <c r="J16">
+        <v>3618.4</v>
+      </c>
+      <c r="K16">
+        <v>971.6</v>
       </c>
       <c r="L16" t="str">
         <v/>
       </c>
       <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
         <v>EXP2201230001</v>
       </c>
-      <c r="N16" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1148,20 +1246,26 @@
       <c r="I17">
         <v>60</v>
       </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
+      <c r="J17">
+        <v>1823.85</v>
+      </c>
+      <c r="K17">
+        <v>512.6</v>
       </c>
       <c r="L17" t="str">
         <v/>
       </c>
       <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
         <v>EXP2202050001</v>
       </c>
-      <c r="N17" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P17" t="str">
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -1192,20 +1296,26 @@
       <c r="I18">
         <v>36</v>
       </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
+      <c r="J18">
+        <v>3106.14</v>
+      </c>
+      <c r="K18">
+        <v>903.21</v>
       </c>
       <c r="L18" t="str">
         <v/>
       </c>
       <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
         <v>EXP2202160001</v>
       </c>
-      <c r="N18" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P18" t="str">
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1236,11 +1346,11 @@
       <c r="I19">
         <v>60</v>
       </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
+      <c r="J19">
+        <v>9999</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1249,7 +1359,13 @@
         <v/>
       </c>
       <c r="N19" t="str">
-        <v>บัญชีเดิม:1801000</v>
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1280,20 +1396,26 @@
       <c r="I20">
         <v>36</v>
       </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
+      <c r="J20">
+        <v>3196.97</v>
+      </c>
+      <c r="K20">
+        <v>961.91</v>
       </c>
       <c r="L20" t="str">
         <v/>
       </c>
       <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
         <v>EXP2202270001</v>
       </c>
-      <c r="N20" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P20" t="str">
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1324,20 +1446,26 @@
       <c r="I21">
         <v>60</v>
       </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
-        <v/>
+      <c r="J21">
+        <v>2454.25</v>
+      </c>
+      <c r="K21">
+        <v>736.4</v>
       </c>
       <c r="L21" t="str">
         <v/>
       </c>
       <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
         <v>EXP2202260002</v>
       </c>
-      <c r="N21" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P21" t="str">
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -1368,11 +1496,11 @@
       <c r="I22">
         <v>60</v>
       </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
+      <c r="J22">
+        <v>2890.02</v>
+      </c>
+      <c r="K22">
+        <v>866.98</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1381,7 +1509,13 @@
         <v/>
       </c>
       <c r="N22" t="str">
-        <v>บัญชีเดิม:1704000</v>
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -1412,11 +1546,11 @@
       <c r="I23">
         <v>60</v>
       </c>
-      <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
+      <c r="J23">
+        <v>3530.04</v>
+      </c>
+      <c r="K23">
+        <v>1058.75</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1425,7 +1559,13 @@
         <v/>
       </c>
       <c r="N23" t="str">
-        <v>บัญชีเดิม:1704000</v>
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -1456,20 +1596,26 @@
       <c r="I24">
         <v>36</v>
       </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
+      <c r="J24">
+        <v>2294.95</v>
+      </c>
+      <c r="K24">
+        <v>695.05</v>
       </c>
       <c r="L24" t="str">
         <v/>
       </c>
       <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
         <v>EXP2203010001</v>
       </c>
-      <c r="N24" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P24" t="str">
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -1500,20 +1646,26 @@
       <c r="I25">
         <v>36</v>
       </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
+      <c r="J25">
+        <v>2141.39</v>
+      </c>
+      <c r="K25">
+        <v>648.61</v>
       </c>
       <c r="L25" t="str">
         <v/>
       </c>
       <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
         <v>EXP2203010002</v>
       </c>
-      <c r="N25" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P25" t="str">
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -1544,20 +1696,26 @@
       <c r="I26">
         <v>36</v>
       </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
+      <c r="J26">
+        <v>2286.65</v>
+      </c>
+      <c r="K26">
+        <v>694.66</v>
       </c>
       <c r="L26" t="str">
         <v/>
       </c>
       <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
         <v>EXP2203020001</v>
       </c>
-      <c r="N26" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P26" t="str">
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1588,20 +1746,26 @@
       <c r="I27">
         <v>60</v>
       </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
+      <c r="J27">
+        <v>4347.41</v>
+      </c>
+      <c r="K27">
+        <v>1344.18</v>
       </c>
       <c r="L27" t="str">
         <v/>
       </c>
       <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
         <v>EXP2203080001</v>
       </c>
-      <c r="N27" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P27" t="str">
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -1632,20 +1796,26 @@
       <c r="I28">
         <v>60</v>
       </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
+      <c r="J28">
+        <v>16730.46</v>
+      </c>
+      <c r="K28">
+        <v>5138.7</v>
       </c>
       <c r="L28" t="str">
         <v/>
       </c>
       <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
         <v>EXP2203060001</v>
       </c>
-      <c r="N28" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P28" t="str">
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1676,20 +1846,26 @@
       <c r="I29">
         <v>60</v>
       </c>
-      <c r="J29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <v/>
+      <c r="J29">
+        <v>9937.86</v>
+      </c>
+      <c r="K29">
+        <v>3052.79</v>
       </c>
       <c r="L29" t="str">
         <v/>
       </c>
       <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
         <v>EXP2203060001</v>
       </c>
-      <c r="N29" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P29" t="str">
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1720,20 +1896,26 @@
       <c r="I30">
         <v>60</v>
       </c>
-      <c r="J30" t="str">
-        <v/>
-      </c>
-      <c r="K30" t="str">
-        <v/>
+      <c r="J30">
+        <v>1808.86</v>
+      </c>
+      <c r="K30">
+        <v>564.97</v>
       </c>
       <c r="L30" t="str">
         <v/>
       </c>
       <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
         <v>EXP2203110001</v>
       </c>
-      <c r="N30" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P30" t="str">
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -1764,20 +1946,26 @@
       <c r="I31">
         <v>60</v>
       </c>
-      <c r="J31" t="str">
-        <v/>
-      </c>
-      <c r="K31" t="str">
-        <v/>
+      <c r="J31">
+        <v>2268.69</v>
+      </c>
+      <c r="K31">
+        <v>712.62</v>
       </c>
       <c r="L31" t="str">
         <v/>
       </c>
       <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
         <v>EXP2203130001</v>
       </c>
-      <c r="N31" t="str">
-        <v>บัญชีเดิม:1706000</v>
+      <c r="P31" t="str">
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -1808,20 +1996,26 @@
       <c r="I32">
         <v>60</v>
       </c>
-      <c r="J32" t="str">
-        <v/>
-      </c>
-      <c r="K32" t="str">
-        <v/>
+      <c r="J32">
+        <v>8625.85</v>
+      </c>
+      <c r="K32">
+        <v>2674.15</v>
       </c>
       <c r="L32" t="str">
         <v/>
       </c>
       <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
         <v>EXP2203090001</v>
       </c>
-      <c r="N32" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P32" t="str">
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -1852,20 +2046,26 @@
       <c r="I33">
         <v>36</v>
       </c>
-      <c r="J33" t="str">
-        <v/>
-      </c>
-      <c r="K33" t="str">
-        <v/>
+      <c r="J33">
+        <v>6790.19</v>
+      </c>
+      <c r="K33">
+        <v>2163.08</v>
       </c>
       <c r="L33" t="str">
         <v/>
       </c>
       <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
         <v>EXP2203180002</v>
       </c>
-      <c r="N33" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P33" t="str">
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -1896,20 +2096,26 @@
       <c r="I34">
         <v>36</v>
       </c>
-      <c r="J34" t="str">
-        <v/>
-      </c>
-      <c r="K34" t="str">
-        <v/>
+      <c r="J34">
+        <v>8498.57</v>
+      </c>
+      <c r="K34">
+        <v>2707.04</v>
       </c>
       <c r="L34" t="str">
         <v/>
       </c>
       <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
         <v>EXP2203180002</v>
       </c>
-      <c r="N34" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P34" t="str">
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -1940,20 +2146,26 @@
       <c r="I35">
         <v>60</v>
       </c>
-      <c r="J35" t="str">
-        <v/>
-      </c>
-      <c r="K35" t="str">
-        <v/>
+      <c r="J35">
+        <v>6013.18</v>
+      </c>
+      <c r="K35">
+        <v>1921.4</v>
       </c>
       <c r="L35" t="str">
         <v/>
       </c>
       <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
         <v>EXP2203190001</v>
       </c>
-      <c r="N35" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P35" t="str">
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -1984,20 +2196,26 @@
       <c r="I36">
         <v>60</v>
       </c>
-      <c r="J36" t="str">
-        <v/>
-      </c>
-      <c r="K36" t="str">
-        <v/>
+      <c r="J36">
+        <v>4695.93</v>
+      </c>
+      <c r="K36">
+        <v>1509.68</v>
       </c>
       <c r="L36" t="str">
         <v/>
       </c>
       <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
         <v>EXP2203210001</v>
       </c>
-      <c r="N36" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P36" t="str">
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -2028,20 +2246,26 @@
       <c r="I37">
         <v>60</v>
       </c>
-      <c r="J37" t="str">
-        <v/>
-      </c>
-      <c r="K37" t="str">
-        <v/>
+      <c r="J37">
+        <v>20367.19</v>
+      </c>
+      <c r="K37">
+        <v>6642.16</v>
       </c>
       <c r="L37" t="str">
         <v/>
       </c>
       <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
         <v>EXP2203260001</v>
       </c>
-      <c r="N37" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P37" t="str">
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -2072,20 +2296,26 @@
       <c r="I38">
         <v>36</v>
       </c>
-      <c r="J38" t="str">
-        <v/>
-      </c>
-      <c r="K38" t="str">
-        <v/>
+      <c r="J38">
+        <v>7019.48</v>
+      </c>
+      <c r="K38">
+        <v>2316.97</v>
       </c>
       <c r="L38" t="str">
         <v/>
       </c>
       <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
         <v>EXP2203300001</v>
       </c>
-      <c r="N38" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P38" t="str">
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -2116,20 +2346,26 @@
       <c r="I39">
         <v>60</v>
       </c>
-      <c r="J39" t="str">
-        <v/>
-      </c>
-      <c r="K39" t="str">
-        <v/>
+      <c r="J39">
+        <v>4522.3</v>
+      </c>
+      <c r="K39">
+        <v>1636.58</v>
       </c>
       <c r="L39" t="str">
         <v/>
       </c>
       <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
         <v>EXP2205010002</v>
       </c>
-      <c r="N39" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P39" t="str">
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -2160,20 +2396,26 @@
       <c r="I40">
         <v>60</v>
       </c>
-      <c r="J40" t="str">
-        <v/>
-      </c>
-      <c r="K40" t="str">
-        <v/>
+      <c r="J40">
+        <v>3069.48</v>
+      </c>
+      <c r="K40">
+        <v>1126.78</v>
       </c>
       <c r="L40" t="str">
         <v/>
       </c>
       <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
         <v>EXP2205060001</v>
       </c>
-      <c r="N40" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P40" t="str">
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -2204,20 +2446,26 @@
       <c r="I41">
         <v>60</v>
       </c>
-      <c r="J41" t="str">
-        <v/>
-      </c>
-      <c r="K41" t="str">
-        <v/>
+      <c r="J41">
+        <v>14290.45</v>
+      </c>
+      <c r="K41">
+        <v>5242.26</v>
       </c>
       <c r="L41" t="str">
         <v/>
       </c>
       <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
         <v>EXP2205060001</v>
       </c>
-      <c r="N41" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P41" t="str">
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -2248,20 +2496,26 @@
       <c r="I42">
         <v>60</v>
       </c>
-      <c r="J42" t="str">
-        <v/>
-      </c>
-      <c r="K42" t="str">
-        <v/>
+      <c r="J42">
+        <v>3388.39</v>
+      </c>
+      <c r="K42">
+        <v>1275.16</v>
       </c>
       <c r="L42" t="str">
         <v/>
       </c>
       <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
         <v>EXP2205150001</v>
       </c>
-      <c r="N42" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P42" t="str">
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -2292,20 +2546,26 @@
       <c r="I43">
         <v>60</v>
       </c>
-      <c r="J43" t="str">
-        <v/>
-      </c>
-      <c r="K43" t="str">
-        <v/>
+      <c r="J43">
+        <v>5018.43</v>
+      </c>
+      <c r="K43">
+        <v>1888.11</v>
       </c>
       <c r="L43" t="str">
         <v/>
       </c>
       <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
         <v>EXP2205150001</v>
       </c>
-      <c r="N43" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P43" t="str">
+        <v/>
       </c>
     </row>
     <row r="44">
@@ -2336,20 +2596,26 @@
       <c r="I44">
         <v>60</v>
       </c>
-      <c r="J44" t="str">
-        <v/>
-      </c>
-      <c r="K44" t="str">
-        <v/>
+      <c r="J44">
+        <v>12051.4</v>
+      </c>
+      <c r="K44">
+        <v>5696.26</v>
       </c>
       <c r="L44" t="str">
         <v/>
       </c>
       <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
         <v>EXP2208100001</v>
       </c>
-      <c r="N44" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P44" t="str">
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -2380,20 +2646,26 @@
       <c r="I45">
         <v>60</v>
       </c>
-      <c r="J45" t="str">
-        <v/>
-      </c>
-      <c r="K45" t="str">
-        <v/>
+      <c r="J45">
+        <v>94042.2</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
       </c>
       <c r="L45" t="str">
         <v/>
       </c>
       <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
         <v>EXP2208160001</v>
       </c>
-      <c r="N45" t="str">
-        <v>บัญชีเดิม:1801000</v>
+      <c r="P45" t="str">
+        <v/>
       </c>
     </row>
     <row r="46">
@@ -2424,20 +2696,26 @@
       <c r="I46">
         <v>60</v>
       </c>
-      <c r="J46" t="str">
-        <v/>
-      </c>
-      <c r="K46" t="str">
-        <v/>
+      <c r="J46">
+        <v>8685.85</v>
+      </c>
+      <c r="K46">
+        <v>4304.8</v>
       </c>
       <c r="L46" t="str">
         <v/>
       </c>
       <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
         <v>EXP2208260001</v>
       </c>
-      <c r="N46" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P46" t="str">
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -2468,20 +2746,26 @@
       <c r="I47">
         <v>60</v>
       </c>
-      <c r="J47" t="str">
-        <v/>
-      </c>
-      <c r="K47" t="str">
-        <v/>
+      <c r="J47">
+        <v>9846.47</v>
+      </c>
+      <c r="K47">
+        <v>5200.26</v>
       </c>
       <c r="L47" t="str">
         <v/>
       </c>
       <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
         <v>EXP2209240001</v>
       </c>
-      <c r="N47" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P47" t="str">
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -2512,20 +2796,26 @@
       <c r="I48">
         <v>60</v>
       </c>
-      <c r="J48" t="str">
-        <v/>
-      </c>
-      <c r="K48" t="str">
-        <v/>
+      <c r="J48">
+        <v>3313.18</v>
+      </c>
+      <c r="K48">
+        <v>1841.03</v>
       </c>
       <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
         <v>สเตเบิ้ล ลายส์</v>
       </c>
-      <c r="M48" t="str">
+      <c r="O48" t="str">
         <v>PA2210150001</v>
       </c>
-      <c r="N48" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P48" t="str">
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -2556,20 +2846,26 @@
       <c r="I49">
         <v>60</v>
       </c>
-      <c r="J49" t="str">
-        <v/>
-      </c>
-      <c r="K49" t="str">
-        <v/>
+      <c r="J49">
+        <v>3238.07</v>
+      </c>
+      <c r="K49">
+        <v>1799.32</v>
       </c>
       <c r="L49" t="str">
         <v/>
       </c>
       <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
         <v>PA2210150002</v>
       </c>
-      <c r="N49" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P49" t="str">
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -2600,20 +2896,26 @@
       <c r="I50">
         <v>60</v>
       </c>
-      <c r="J50" t="str">
-        <v/>
-      </c>
-      <c r="K50" t="str">
-        <v/>
+      <c r="J50">
+        <v>3238.07</v>
+      </c>
+      <c r="K50">
+        <v>1799.31</v>
       </c>
       <c r="L50" t="str">
         <v/>
       </c>
       <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
         <v>PA2210240001</v>
       </c>
-      <c r="N50" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P50" t="str">
+        <v/>
       </c>
     </row>
     <row r="51">
@@ -2644,20 +2946,26 @@
       <c r="I51">
         <v>60</v>
       </c>
-      <c r="J51" t="str">
-        <v/>
-      </c>
-      <c r="K51" t="str">
-        <v/>
+      <c r="J51">
+        <v>32241.9</v>
+      </c>
+      <c r="K51">
+        <v>14484.27</v>
       </c>
       <c r="L51" t="str">
         <v/>
       </c>
       <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
         <v>EXP2207210001</v>
       </c>
-      <c r="N51" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P51" t="str">
+        <v/>
       </c>
     </row>
     <row r="52">
@@ -2688,11 +2996,11 @@
       <c r="I52">
         <v>60</v>
       </c>
-      <c r="J52" t="str">
-        <v/>
-      </c>
-      <c r="K52" t="str">
-        <v/>
+      <c r="J52">
+        <v>23262.13</v>
+      </c>
+      <c r="K52">
+        <v>14868.71</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2701,7 +3009,13 @@
         <v/>
       </c>
       <c r="N52" t="str">
-        <v>บัญชีเดิม:1704000</v>
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -2732,20 +3046,26 @@
       <c r="I53">
         <v>60</v>
       </c>
-      <c r="J53" t="str">
-        <v/>
-      </c>
-      <c r="K53" t="str">
-        <v/>
+      <c r="J53">
+        <v>1839.94</v>
+      </c>
+      <c r="K53">
+        <v>1187.85</v>
       </c>
       <c r="L53" t="str">
         <v/>
       </c>
       <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
         <v>EXP2212180002</v>
       </c>
-      <c r="N53" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P53" t="str">
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -2776,20 +3096,26 @@
       <c r="I54">
         <v>60</v>
       </c>
-      <c r="J54" t="str">
-        <v/>
-      </c>
-      <c r="K54" t="str">
-        <v/>
+      <c r="J54">
+        <v>12303.06</v>
+      </c>
+      <c r="K54">
+        <v>8083.95</v>
       </c>
       <c r="L54" t="str">
         <v/>
       </c>
       <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
         <v>PA2212260001</v>
       </c>
-      <c r="N54" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P54" t="str">
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -2820,20 +3146,26 @@
       <c r="I55">
         <v>60</v>
       </c>
-      <c r="J55" t="str">
-        <v/>
-      </c>
-      <c r="K55" t="str">
-        <v/>
+      <c r="J55">
+        <v>9297.86</v>
+      </c>
+      <c r="K55">
+        <v>6496.53</v>
       </c>
       <c r="L55" t="str">
         <v/>
       </c>
       <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
         <v>PA2301220001</v>
       </c>
-      <c r="N55" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P55" t="str">
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -2864,20 +3196,26 @@
       <c r="I56">
         <v>60</v>
       </c>
-      <c r="J56" t="str">
-        <v/>
-      </c>
-      <c r="K56" t="str">
-        <v/>
+      <c r="J56">
+        <v>641.98</v>
+      </c>
+      <c r="K56">
+        <v>470.17</v>
       </c>
       <c r="L56" t="str">
         <v/>
       </c>
       <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
         <v>EXP2302110001</v>
       </c>
-      <c r="N56" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P56" t="str">
+        <v/>
       </c>
     </row>
     <row r="57">
@@ -2908,20 +3246,26 @@
       <c r="I57">
         <v>60</v>
       </c>
-      <c r="J57" t="str">
-        <v/>
-      </c>
-      <c r="K57" t="str">
-        <v/>
+      <c r="J57">
+        <v>1160.83</v>
+      </c>
+      <c r="K57">
+        <v>684.97</v>
       </c>
       <c r="L57" t="str">
         <v/>
       </c>
       <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
         <v>EXP2211090003</v>
       </c>
-      <c r="N57" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P57" t="str">
+        <v/>
       </c>
     </row>
     <row r="58">
@@ -2952,20 +3296,26 @@
       <c r="I58">
         <v>36</v>
       </c>
-      <c r="J58" t="str">
-        <v/>
-      </c>
-      <c r="K58" t="str">
-        <v/>
+      <c r="J58">
+        <v>2378.1</v>
+      </c>
+      <c r="K58">
+        <v>1967.69</v>
       </c>
       <c r="L58" t="str">
         <v/>
       </c>
       <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
         <v>PA2304070001</v>
       </c>
-      <c r="N58" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P58" t="str">
+        <v/>
       </c>
     </row>
     <row r="59">
@@ -2996,20 +3346,26 @@
       <c r="I59">
         <v>60</v>
       </c>
-      <c r="J59" t="str">
-        <v/>
-      </c>
-      <c r="K59" t="str">
-        <v/>
+      <c r="J59">
+        <v>2756.64</v>
+      </c>
+      <c r="K59">
+        <v>2280.74</v>
       </c>
       <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
         <v>บริษัท อินเด็กซ์ ลิฟวิ่งมอลล์ จำกัด (มหาชน)</v>
       </c>
-      <c r="M59" t="str">
+      <c r="O59" t="str">
         <v>PA2304070002</v>
       </c>
-      <c r="N59" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P59" t="str">
+        <v/>
       </c>
     </row>
     <row r="60">
@@ -3040,20 +3396,26 @@
       <c r="I60">
         <v>60</v>
       </c>
-      <c r="J60" t="str">
-        <v/>
-      </c>
-      <c r="K60" t="str">
-        <v/>
+      <c r="J60">
+        <v>3933.18</v>
+      </c>
+      <c r="K60">
+        <v>3253.74</v>
       </c>
       <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
         <v>บริษัท อินเด็กซ์ ลิฟวิ่งมอลล์ จำกัด (มหาชน)</v>
       </c>
-      <c r="M60" t="str">
+      <c r="O60" t="str">
         <v>PA2304070002</v>
       </c>
-      <c r="N60" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P60" t="str">
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -3084,20 +3446,26 @@
       <c r="I61">
         <v>36</v>
       </c>
-      <c r="J61" t="str">
-        <v/>
-      </c>
-      <c r="K61" t="str">
-        <v/>
+      <c r="J61">
+        <v>9713.55</v>
+      </c>
+      <c r="K61">
+        <v>8034.11</v>
       </c>
       <c r="L61" t="str">
         <v/>
       </c>
       <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
         <v>PA2304070003</v>
       </c>
-      <c r="N61" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P61" t="str">
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -3128,11 +3496,11 @@
       <c r="I62">
         <v>60</v>
       </c>
-      <c r="J62" t="str">
-        <v/>
-      </c>
-      <c r="K62" t="str">
-        <v/>
+      <c r="J62">
+        <v>3324999</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
       </c>
       <c r="L62" t="str">
         <v/>
@@ -3141,7 +3509,13 @@
         <v/>
       </c>
       <c r="N62" t="str">
-        <v>บัญชีเดิม:1801000</v>
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -3172,11 +3546,11 @@
       <c r="I63">
         <v>60</v>
       </c>
-      <c r="J63" t="str">
-        <v/>
-      </c>
-      <c r="K63" t="str">
-        <v/>
+      <c r="J63">
+        <v>1872020.24</v>
+      </c>
+      <c r="K63">
+        <v>1417979.76</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3185,7 +3559,13 @@
         <v/>
       </c>
       <c r="N63" t="str">
-        <v>บัญชีเดิม:1706000</v>
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -3216,20 +3596,26 @@
       <c r="I64">
         <v>60</v>
       </c>
-      <c r="J64" t="str">
-        <v/>
-      </c>
-      <c r="K64" t="str">
-        <v/>
+      <c r="J64">
+        <v>891.87</v>
+      </c>
+      <c r="K64">
+        <v>835.23</v>
       </c>
       <c r="L64" t="str">
         <v/>
       </c>
       <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
         <v>PA2306020004</v>
       </c>
-      <c r="N64" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P64" t="str">
+        <v/>
       </c>
     </row>
     <row r="65">
@@ -3260,20 +3646,26 @@
       <c r="I65">
         <v>60</v>
       </c>
-      <c r="J65" t="str">
-        <v/>
-      </c>
-      <c r="K65" t="str">
-        <v/>
+      <c r="J65">
+        <v>4279.33</v>
+      </c>
+      <c r="K65">
+        <v>3748.71</v>
       </c>
       <c r="L65" t="str">
         <v/>
       </c>
       <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
         <v>PA2305030001</v>
       </c>
-      <c r="N65" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P65" t="str">
+        <v/>
       </c>
     </row>
     <row r="66">
@@ -3304,20 +3696,26 @@
       <c r="I66">
         <v>60</v>
       </c>
-      <c r="J66" t="str">
-        <v/>
-      </c>
-      <c r="K66" t="str">
-        <v/>
+      <c r="J66">
+        <v>16457.01</v>
+      </c>
+      <c r="K66">
+        <v>15496.13</v>
       </c>
       <c r="L66" t="str">
         <v/>
       </c>
       <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
         <v>PA2306050001</v>
       </c>
-      <c r="N66" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P66" t="str">
+        <v/>
       </c>
     </row>
     <row r="67">
@@ -3348,20 +3746,26 @@
       <c r="I67">
         <v>60</v>
       </c>
-      <c r="J67" t="str">
-        <v/>
-      </c>
-      <c r="K67" t="str">
-        <v/>
+      <c r="J67">
+        <v>4968.9</v>
+      </c>
+      <c r="K67">
+        <v>4741.38</v>
       </c>
       <c r="L67" t="str">
         <v/>
       </c>
       <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
         <v>PA2306110001</v>
       </c>
-      <c r="N67" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P67" t="str">
+        <v/>
       </c>
     </row>
     <row r="68">
@@ -3392,20 +3796,26 @@
       <c r="I68">
         <v>60</v>
       </c>
-      <c r="J68" t="str">
-        <v/>
-      </c>
-      <c r="K68" t="str">
-        <v/>
+      <c r="J68">
+        <v>4299.3</v>
+      </c>
+      <c r="K68">
+        <v>4102.57</v>
       </c>
       <c r="L68" t="str">
         <v/>
       </c>
       <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
         <v>PA2306110002</v>
       </c>
-      <c r="N68" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P68" t="str">
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -3436,20 +3846,26 @@
       <c r="I69">
         <v>60</v>
       </c>
-      <c r="J69" t="str">
-        <v/>
-      </c>
-      <c r="K69" t="str">
-        <v/>
+      <c r="J69">
+        <v>5143.34</v>
+      </c>
+      <c r="K69">
+        <v>5071.66</v>
       </c>
       <c r="L69" t="str">
         <v/>
       </c>
       <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
         <v>PA2306260001</v>
       </c>
-      <c r="N69" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P69" t="str">
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -3480,20 +3896,26 @@
       <c r="I70">
         <v>60</v>
       </c>
-      <c r="J70" t="str">
-        <v/>
-      </c>
-      <c r="K70" t="str">
-        <v/>
+      <c r="J70">
+        <v>2922.02</v>
+      </c>
+      <c r="K70">
+        <v>2964.9</v>
       </c>
       <c r="L70" t="str">
         <v/>
       </c>
       <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
         <v>PA2307090001</v>
       </c>
-      <c r="N70" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P70" t="str">
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -3524,20 +3946,26 @@
       <c r="I71">
         <v>60</v>
       </c>
-      <c r="J71" t="str">
-        <v/>
-      </c>
-      <c r="K71" t="str">
-        <v/>
+      <c r="J71">
+        <v>15303.27</v>
+      </c>
+      <c r="K71">
+        <v>14696.73</v>
       </c>
       <c r="L71" t="str">
         <v/>
       </c>
       <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
         <v>PA2306140001</v>
       </c>
-      <c r="N71" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P71" t="str">
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -3568,20 +3996,26 @@
       <c r="I72">
         <v>60</v>
       </c>
-      <c r="J72" t="str">
-        <v/>
-      </c>
-      <c r="K72" t="str">
-        <v/>
+      <c r="J72">
+        <v>8671.63</v>
+      </c>
+      <c r="K72">
+        <v>8328.37</v>
       </c>
       <c r="L72" t="str">
         <v/>
       </c>
       <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
         <v>PA2306140001</v>
       </c>
-      <c r="N72" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P72" t="str">
+        <v/>
       </c>
     </row>
     <row r="73">
@@ -3612,20 +4046,26 @@
       <c r="I73">
         <v>60</v>
       </c>
-      <c r="J73" t="str">
-        <v/>
-      </c>
-      <c r="K73" t="str">
-        <v/>
+      <c r="J73">
+        <v>1234.73</v>
+      </c>
+      <c r="K73">
+        <v>1286.77</v>
       </c>
       <c r="L73" t="str">
         <v/>
       </c>
       <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
         <v>PA2307210001</v>
       </c>
-      <c r="N73" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P73" t="str">
+        <v/>
       </c>
     </row>
     <row r="74">
@@ -3656,20 +4096,26 @@
       <c r="I74">
         <v>60</v>
       </c>
-      <c r="J74" t="str">
-        <v/>
-      </c>
-      <c r="K74" t="str">
-        <v/>
+      <c r="J74">
+        <v>11375.92</v>
+      </c>
+      <c r="K74">
+        <v>12736.23</v>
       </c>
       <c r="L74" t="str">
         <v/>
       </c>
       <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
         <v>EXP2308230001</v>
       </c>
-      <c r="N74" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P74" t="str">
+        <v/>
       </c>
     </row>
     <row r="75">
@@ -3700,20 +4146,26 @@
       <c r="I75">
         <v>60</v>
       </c>
-      <c r="J75" t="str">
-        <v/>
-      </c>
-      <c r="K75" t="str">
-        <v/>
+      <c r="J75">
+        <v>24189.77</v>
+      </c>
+      <c r="K75">
+        <v>27380.32</v>
       </c>
       <c r="L75" t="str">
         <v/>
       </c>
       <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
         <v>PA2308280001</v>
       </c>
-      <c r="N75" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P75" t="str">
+        <v/>
       </c>
     </row>
     <row r="76">
@@ -3744,20 +4196,26 @@
       <c r="I76">
         <v>60</v>
       </c>
-      <c r="J76" t="str">
-        <v/>
-      </c>
-      <c r="K76" t="str">
-        <v/>
+      <c r="J76">
+        <v>14406.08</v>
+      </c>
+      <c r="K76">
+        <v>17229.43</v>
       </c>
       <c r="L76" t="str">
         <v/>
       </c>
       <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
         <v>PA2309220001</v>
       </c>
-      <c r="N76" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P76" t="str">
+        <v/>
       </c>
     </row>
     <row r="77">
@@ -3788,20 +4246,26 @@
       <c r="I77">
         <v>60</v>
       </c>
-      <c r="J77" t="str">
-        <v/>
-      </c>
-      <c r="K77" t="str">
-        <v/>
+      <c r="J77">
+        <v>17257.6</v>
+      </c>
+      <c r="K77">
+        <v>20639.6</v>
       </c>
       <c r="L77" t="str">
         <v/>
       </c>
       <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
         <v>PA2309220002</v>
       </c>
-      <c r="N77" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P77" t="str">
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -3832,20 +4296,26 @@
       <c r="I78">
         <v>60</v>
       </c>
-      <c r="J78" t="str">
-        <v/>
-      </c>
-      <c r="K78" t="str">
-        <v/>
+      <c r="J78">
+        <v>8018.2</v>
+      </c>
+      <c r="K78">
+        <v>9761.01</v>
       </c>
       <c r="L78" t="str">
         <v/>
       </c>
       <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
         <v>PA2309300001</v>
       </c>
-      <c r="N78" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P78" t="str">
+        <v/>
       </c>
     </row>
     <row r="79">
@@ -3876,20 +4346,26 @@
       <c r="I79">
         <v>60</v>
       </c>
-      <c r="J79" t="str">
-        <v/>
-      </c>
-      <c r="K79" t="str">
-        <v/>
+      <c r="J79">
+        <v>40330.92</v>
+      </c>
+      <c r="K79">
+        <v>49201.79</v>
       </c>
       <c r="L79" t="str">
         <v/>
       </c>
       <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
         <v>PA2310010001</v>
       </c>
-      <c r="N79" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P79" t="str">
+        <v/>
       </c>
     </row>
     <row r="80">
@@ -3920,20 +4396,26 @@
       <c r="I80">
         <v>36</v>
       </c>
-      <c r="J80" t="str">
-        <v/>
-      </c>
-      <c r="K80" t="str">
-        <v/>
+      <c r="J80">
+        <v>7056.67</v>
+      </c>
+      <c r="K80">
+        <v>8821.83</v>
       </c>
       <c r="L80" t="str">
         <v/>
       </c>
       <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
         <v>PA2310120001</v>
       </c>
-      <c r="N80" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P80" t="str">
+        <v/>
       </c>
     </row>
     <row r="81">
@@ -3964,20 +4446,26 @@
       <c r="I81">
         <v>60</v>
       </c>
-      <c r="J81" t="str">
-        <v/>
-      </c>
-      <c r="K81" t="str">
-        <v/>
+      <c r="J81">
+        <v>1889.48</v>
+      </c>
+      <c r="K81">
+        <v>2362.86</v>
       </c>
       <c r="L81" t="str">
         <v/>
       </c>
       <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
         <v>PA2310120001</v>
       </c>
-      <c r="N81" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P81" t="str">
+        <v/>
       </c>
     </row>
     <row r="82">
@@ -4008,20 +4496,26 @@
       <c r="I82">
         <v>36</v>
       </c>
-      <c r="J82" t="str">
-        <v/>
-      </c>
-      <c r="K82" t="str">
-        <v/>
+      <c r="J82">
+        <v>7444.43</v>
+      </c>
+      <c r="K82">
+        <v>9368.65</v>
       </c>
       <c r="L82" t="str">
         <v/>
       </c>
       <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
         <v>PA2310150001</v>
       </c>
-      <c r="N82" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P82" t="str">
+        <v/>
       </c>
     </row>
     <row r="83">
@@ -4052,20 +4546,26 @@
       <c r="I83">
         <v>60</v>
       </c>
-      <c r="J83" t="str">
-        <v/>
-      </c>
-      <c r="K83" t="str">
-        <v/>
+      <c r="J83">
+        <v>1923.89</v>
+      </c>
+      <c r="K83">
+        <v>2421.91</v>
       </c>
       <c r="L83" t="str">
         <v/>
       </c>
       <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
         <v>PA2310150001</v>
       </c>
-      <c r="N83" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P83" t="str">
+        <v/>
       </c>
     </row>
     <row r="84">
@@ -4096,20 +4596,26 @@
       <c r="I84">
         <v>36</v>
       </c>
-      <c r="J84" t="str">
-        <v/>
-      </c>
-      <c r="K84" t="str">
-        <v/>
+      <c r="J84">
+        <v>7454.96</v>
+      </c>
+      <c r="K84">
+        <v>9361.12</v>
       </c>
       <c r="L84" t="str">
         <v/>
       </c>
       <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
         <v>PA2310140001</v>
       </c>
-      <c r="N84" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P84" t="str">
+        <v/>
       </c>
     </row>
     <row r="85">
@@ -4140,20 +4646,26 @@
       <c r="I85">
         <v>60</v>
       </c>
-      <c r="J85" t="str">
-        <v/>
-      </c>
-      <c r="K85" t="str">
-        <v/>
+      <c r="J85">
+        <v>8124.04</v>
+      </c>
+      <c r="K85">
+        <v>10044.18</v>
       </c>
       <c r="L85" t="str">
         <v/>
       </c>
       <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
         <v>PA2310070001</v>
       </c>
-      <c r="N85" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P85" t="str">
+        <v/>
       </c>
     </row>
     <row r="86">
@@ -4184,20 +4696,26 @@
       <c r="I86">
         <v>60</v>
       </c>
-      <c r="J86" t="str">
-        <v/>
-      </c>
-      <c r="K86" t="str">
-        <v/>
+      <c r="J86">
+        <v>1926.27</v>
+      </c>
+      <c r="K86">
+        <v>2419.53</v>
       </c>
       <c r="L86" t="str">
         <v/>
       </c>
       <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
         <v>PA2310140001</v>
       </c>
-      <c r="N86" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P86" t="str">
+        <v/>
       </c>
     </row>
     <row r="87">
@@ -4228,20 +4746,26 @@
       <c r="I87">
         <v>60</v>
       </c>
-      <c r="J87" t="str">
-        <v/>
-      </c>
-      <c r="K87" t="str">
-        <v/>
+      <c r="J87">
+        <v>9900.7</v>
+      </c>
+      <c r="K87">
+        <v>11999.3</v>
       </c>
       <c r="L87" t="str">
         <v/>
       </c>
       <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
         <v>PA2309280001</v>
       </c>
-      <c r="N87" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P87" t="str">
+        <v/>
       </c>
     </row>
     <row r="88">
@@ -4272,20 +4796,26 @@
       <c r="I88">
         <v>60</v>
       </c>
-      <c r="J88" t="str">
-        <v/>
-      </c>
-      <c r="K88" t="str">
-        <v/>
+      <c r="J88">
+        <v>10234.22</v>
+      </c>
+      <c r="K88">
+        <v>12186.34</v>
       </c>
       <c r="L88" t="str">
         <v/>
       </c>
       <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
         <v>PA2309200001</v>
       </c>
-      <c r="N88" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P88" t="str">
+        <v/>
       </c>
     </row>
     <row r="89">
@@ -4316,20 +4846,26 @@
       <c r="I89">
         <v>60</v>
       </c>
-      <c r="J89" t="str">
-        <v/>
-      </c>
-      <c r="K89" t="str">
-        <v/>
+      <c r="J89">
+        <v>11997.74</v>
+      </c>
+      <c r="K89">
+        <v>14702.26</v>
       </c>
       <c r="L89" t="str">
         <v/>
       </c>
       <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
         <v>PA2310030001</v>
       </c>
-      <c r="N89" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P89" t="str">
+        <v/>
       </c>
     </row>
     <row r="90">
@@ -4360,20 +4896,26 @@
       <c r="I90">
         <v>60</v>
       </c>
-      <c r="J90" t="str">
-        <v/>
-      </c>
-      <c r="K90" t="str">
-        <v/>
+      <c r="J90">
+        <v>20135.98</v>
+      </c>
+      <c r="K90">
+        <v>25564.95</v>
       </c>
       <c r="L90" t="str">
         <v/>
       </c>
       <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
         <v>PA2310190001</v>
       </c>
-      <c r="N90" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P90" t="str">
+        <v/>
       </c>
     </row>
     <row r="91">
@@ -4404,20 +4946,26 @@
       <c r="I91">
         <v>60</v>
       </c>
-      <c r="J91" t="str">
-        <v/>
-      </c>
-      <c r="K91" t="str">
-        <v/>
+      <c r="J91">
+        <v>684.51</v>
+      </c>
+      <c r="K91">
+        <v>949.13</v>
       </c>
       <c r="L91" t="str">
         <v/>
       </c>
       <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
         <v>EXP2311270001</v>
       </c>
-      <c r="N91" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P91" t="str">
+        <v/>
       </c>
     </row>
     <row r="92">
@@ -4448,20 +4996,26 @@
       <c r="I92">
         <v>60</v>
       </c>
-      <c r="J92" t="str">
-        <v/>
-      </c>
-      <c r="K92" t="str">
-        <v/>
+      <c r="J92">
+        <v>3934.48</v>
+      </c>
+      <c r="K92">
+        <v>5401.97</v>
       </c>
       <c r="L92" t="str">
         <v/>
       </c>
       <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
         <v>PA2311230001</v>
       </c>
-      <c r="N92" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P92" t="str">
+        <v/>
       </c>
     </row>
     <row r="93">
@@ -4492,20 +5046,26 @@
       <c r="I93">
         <v>60</v>
       </c>
-      <c r="J93" t="str">
-        <v/>
-      </c>
-      <c r="K93" t="str">
-        <v/>
+      <c r="J93">
+        <v>1099.33</v>
+      </c>
+      <c r="K93">
+        <v>1554.88</v>
       </c>
       <c r="L93" t="str">
+        <v/>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
         <v>บริษัท แอดไวซ์ ไอที อินฟินิท จำกัด</v>
       </c>
-      <c r="M93" t="str">
+      <c r="O93" t="str">
         <v>EXP2312060003</v>
       </c>
-      <c r="N93" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P93" t="str">
+        <v/>
       </c>
     </row>
     <row r="94">
@@ -4536,20 +5096,26 @@
       <c r="I94">
         <v>36</v>
       </c>
-      <c r="J94" t="str">
-        <v/>
-      </c>
-      <c r="K94" t="str">
-        <v/>
+      <c r="J94">
+        <v>1572.57</v>
+      </c>
+      <c r="K94">
+        <v>2259.21</v>
       </c>
       <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M94" t="str">
+      <c r="O94" t="str">
         <v>PA2312130001</v>
       </c>
-      <c r="N94" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P94" t="str">
+        <v/>
       </c>
     </row>
     <row r="95">
@@ -4580,20 +5146,26 @@
       <c r="I95">
         <v>36</v>
       </c>
-      <c r="J95" t="str">
-        <v/>
-      </c>
-      <c r="K95" t="str">
-        <v/>
+      <c r="J95">
+        <v>6790.25</v>
+      </c>
+      <c r="K95">
+        <v>9751.8</v>
       </c>
       <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M95" t="str">
+      <c r="O95" t="str">
         <v>PA2312130001</v>
       </c>
-      <c r="N95" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P95" t="str">
+        <v/>
       </c>
     </row>
     <row r="96">
@@ -4624,20 +5196,26 @@
       <c r="I96">
         <v>36</v>
       </c>
-      <c r="J96" t="str">
-        <v/>
-      </c>
-      <c r="K96" t="str">
-        <v/>
+      <c r="J96">
+        <v>6792.2</v>
+      </c>
+      <c r="K96">
+        <v>9843.31</v>
       </c>
       <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M96" t="str">
+      <c r="O96" t="str">
         <v>PA2312170001</v>
       </c>
-      <c r="N96" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P96" t="str">
+        <v/>
       </c>
     </row>
     <row r="97">
@@ -4668,20 +5246,26 @@
       <c r="I97">
         <v>36</v>
       </c>
-      <c r="J97" t="str">
-        <v/>
-      </c>
-      <c r="K97" t="str">
-        <v/>
+      <c r="J97">
+        <v>6827.89</v>
+      </c>
+      <c r="K97">
+        <v>9985.19</v>
       </c>
       <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M97" t="str">
+      <c r="O97" t="str">
         <v>PA2312210001</v>
       </c>
-      <c r="N97" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P97" t="str">
+        <v/>
       </c>
     </row>
     <row r="98">
@@ -4712,20 +5296,26 @@
       <c r="I98">
         <v>36</v>
       </c>
-      <c r="J98" t="str">
-        <v/>
-      </c>
-      <c r="K98" t="str">
-        <v/>
+      <c r="J98">
+        <v>1589.96</v>
+      </c>
+      <c r="K98">
+        <v>2325.93</v>
       </c>
       <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M98" t="str">
+      <c r="O98" t="str">
         <v>PA2312210001</v>
       </c>
-      <c r="N98" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P98" t="str">
+        <v/>
       </c>
     </row>
     <row r="99">
@@ -4756,20 +5346,26 @@
       <c r="I99">
         <v>60</v>
       </c>
-      <c r="J99" t="str">
-        <v/>
-      </c>
-      <c r="K99" t="str">
-        <v/>
+      <c r="J99">
+        <v>2551</v>
+      </c>
+      <c r="K99">
+        <v>3526.5</v>
       </c>
       <c r="L99" t="str">
         <v/>
       </c>
       <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
         <v>PA2311260001</v>
       </c>
-      <c r="N99" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P99" t="str">
+        <v/>
       </c>
     </row>
     <row r="100">
@@ -4800,20 +5396,26 @@
       <c r="I100">
         <v>60</v>
       </c>
-      <c r="J100" t="str">
-        <v/>
-      </c>
-      <c r="K100" t="str">
-        <v/>
+      <c r="J100">
+        <v>2742.1</v>
+      </c>
+      <c r="K100">
+        <v>3790.61</v>
       </c>
       <c r="L100" t="str">
         <v/>
       </c>
       <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
         <v>PA2311260004</v>
       </c>
-      <c r="N100" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P100" t="str">
+        <v/>
       </c>
     </row>
     <row r="101">
@@ -4844,20 +5446,26 @@
       <c r="I101">
         <v>60</v>
       </c>
-      <c r="J101" t="str">
-        <v/>
-      </c>
-      <c r="K101" t="str">
-        <v/>
+      <c r="J101">
+        <v>1353.19</v>
+      </c>
+      <c r="K101">
+        <v>1871.11</v>
       </c>
       <c r="L101" t="str">
         <v/>
       </c>
       <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
         <v>PA2311260003</v>
       </c>
-      <c r="N101" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P101" t="str">
+        <v/>
       </c>
     </row>
     <row r="102">
@@ -4888,20 +5496,26 @@
       <c r="I102">
         <v>36</v>
       </c>
-      <c r="J102" t="str">
-        <v/>
-      </c>
-      <c r="K102" t="str">
-        <v/>
+      <c r="J102">
+        <v>9011.86</v>
+      </c>
+      <c r="K102">
+        <v>14343.28</v>
       </c>
       <c r="L102" t="str">
         <v/>
       </c>
       <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
         <v>PA2401270001</v>
       </c>
-      <c r="N102" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P102" t="str">
+        <v/>
       </c>
     </row>
     <row r="103">
@@ -4932,20 +5546,26 @@
       <c r="I103">
         <v>36</v>
       </c>
-      <c r="J103" t="str">
-        <v/>
-      </c>
-      <c r="K103" t="str">
-        <v/>
+      <c r="J103">
+        <v>1439.05</v>
+      </c>
+      <c r="K103">
+        <v>2383.38</v>
       </c>
       <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M103" t="str">
+      <c r="O103" t="str">
         <v>PA2402130001</v>
       </c>
-      <c r="N103" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P103" t="str">
+        <v/>
       </c>
     </row>
     <row r="104">
@@ -4976,20 +5596,26 @@
       <c r="I104">
         <v>36</v>
       </c>
-      <c r="J104" t="str">
-        <v/>
-      </c>
-      <c r="K104" t="str">
-        <v/>
+      <c r="J104">
+        <v>6682.93</v>
+      </c>
+      <c r="K104">
+        <v>11064.74</v>
       </c>
       <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M104" t="str">
+      <c r="O104" t="str">
         <v>PA2402130001</v>
       </c>
-      <c r="N104" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P104" t="str">
+        <v/>
       </c>
     </row>
     <row r="105">
@@ -5020,20 +5646,26 @@
       <c r="I105">
         <v>36</v>
       </c>
-      <c r="J105" t="str">
-        <v/>
-      </c>
-      <c r="K105" t="str">
-        <v/>
+      <c r="J105">
+        <v>8020.29</v>
+      </c>
+      <c r="K105">
+        <v>13278.77</v>
       </c>
       <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M105" t="str">
+      <c r="O105" t="str">
         <v>PA2402130001</v>
       </c>
-      <c r="N105" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P105" t="str">
+        <v/>
       </c>
     </row>
     <row r="106">
@@ -5064,20 +5696,26 @@
       <c r="I106">
         <v>60</v>
       </c>
-      <c r="J106" t="str">
-        <v/>
-      </c>
-      <c r="K106" t="str">
-        <v/>
+      <c r="J106">
+        <v>1030.29</v>
+      </c>
+      <c r="K106">
+        <v>1726.71</v>
       </c>
       <c r="L106" t="str">
         <v/>
       </c>
       <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
         <v>EXP2402180002</v>
       </c>
-      <c r="N106" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P106" t="str">
+        <v/>
       </c>
     </row>
     <row r="107">
@@ -5108,20 +5746,26 @@
       <c r="I107">
         <v>60</v>
       </c>
-      <c r="J107" t="str">
-        <v/>
-      </c>
-      <c r="K107" t="str">
-        <v/>
+      <c r="J107">
+        <v>13897.09</v>
+      </c>
+      <c r="K107">
+        <v>23607.58</v>
       </c>
       <c r="L107" t="str">
         <v/>
       </c>
       <c r="M107" t="str">
+        <v/>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
         <v>PA2402240001</v>
       </c>
-      <c r="N107" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P107" t="str">
+        <v/>
       </c>
     </row>
     <row r="108">
@@ -5152,20 +5796,26 @@
       <c r="I108">
         <v>36</v>
       </c>
-      <c r="J108" t="str">
-        <v/>
-      </c>
-      <c r="K108" t="str">
-        <v/>
+      <c r="J108">
+        <v>5160.16</v>
+      </c>
+      <c r="K108">
+        <v>8849.19</v>
       </c>
       <c r="L108" t="str">
         <v/>
       </c>
       <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
         <v>EXP2402280001</v>
       </c>
-      <c r="N108" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P108" t="str">
+        <v/>
       </c>
     </row>
     <row r="109">
@@ -5196,20 +5846,26 @@
       <c r="I109">
         <v>36</v>
       </c>
-      <c r="J109" t="str">
-        <v/>
-      </c>
-      <c r="K109" t="str">
-        <v/>
+      <c r="J109">
+        <v>1404.26</v>
+      </c>
+      <c r="K109">
+        <v>2418.16</v>
       </c>
       <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M109" t="str">
+      <c r="O109" t="str">
         <v>PA2403010001</v>
       </c>
-      <c r="N109" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P109" t="str">
+        <v/>
       </c>
     </row>
     <row r="110">
@@ -5240,20 +5896,26 @@
       <c r="I110">
         <v>36</v>
       </c>
-      <c r="J110" t="str">
-        <v/>
-      </c>
-      <c r="K110" t="str">
-        <v/>
+      <c r="J110">
+        <v>1404.26</v>
+      </c>
+      <c r="K110">
+        <v>2418.17</v>
       </c>
       <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M110" t="str">
+      <c r="O110" t="str">
         <v>PA2403010001</v>
       </c>
-      <c r="N110" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P110" t="str">
+        <v/>
       </c>
     </row>
     <row r="111">
@@ -5284,20 +5946,26 @@
       <c r="I111">
         <v>36</v>
       </c>
-      <c r="J111" t="str">
-        <v/>
-      </c>
-      <c r="K111" t="str">
-        <v/>
+      <c r="J111">
+        <v>7038.91</v>
+      </c>
+      <c r="K111">
+        <v>12117.16</v>
       </c>
       <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M111" t="str">
+      <c r="O111" t="str">
         <v>PA2403010001</v>
       </c>
-      <c r="N111" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P111" t="str">
+        <v/>
       </c>
     </row>
     <row r="112">
@@ -5328,20 +5996,26 @@
       <c r="I112">
         <v>60</v>
       </c>
-      <c r="J112" t="str">
-        <v/>
-      </c>
-      <c r="K112" t="str">
-        <v/>
+      <c r="J112">
+        <v>10751.19</v>
+      </c>
+      <c r="K112">
+        <v>18594.6</v>
       </c>
       <c r="L112" t="str">
         <v/>
       </c>
       <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
         <v>PA2403030001</v>
       </c>
-      <c r="N112" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P112" t="str">
+        <v/>
       </c>
     </row>
     <row r="113">
@@ -5372,20 +6046,26 @@
       <c r="I113">
         <v>60</v>
       </c>
-      <c r="J113" t="str">
-        <v/>
-      </c>
-      <c r="K113" t="str">
-        <v/>
+      <c r="J113">
+        <v>9583.32</v>
+      </c>
+      <c r="K113">
+        <v>16771.82</v>
       </c>
       <c r="L113" t="str">
         <v/>
       </c>
       <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
         <v>PA2403080001</v>
       </c>
-      <c r="N113" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P113" t="str">
+        <v/>
       </c>
     </row>
     <row r="114">
@@ -5416,20 +6096,26 @@
       <c r="I114">
         <v>60</v>
       </c>
-      <c r="J114" t="str">
-        <v/>
-      </c>
-      <c r="K114" t="str">
-        <v/>
+      <c r="J114">
+        <v>4297.89</v>
+      </c>
+      <c r="K114">
+        <v>7927.34</v>
       </c>
       <c r="L114" t="str">
         <v/>
       </c>
       <c r="M114" t="str">
+        <v/>
+      </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
         <v>PA2403300001</v>
       </c>
-      <c r="N114" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P114" t="str">
+        <v/>
       </c>
     </row>
     <row r="115">
@@ -5460,20 +6146,26 @@
       <c r="I115">
         <v>60</v>
       </c>
-      <c r="J115" t="str">
-        <v/>
-      </c>
-      <c r="K115" t="str">
-        <v/>
+      <c r="J115">
+        <v>13319.51</v>
+      </c>
+      <c r="K115">
+        <v>24624.42</v>
       </c>
       <c r="L115" t="str">
         <v/>
       </c>
       <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
         <v>PA2403310001</v>
       </c>
-      <c r="N115" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P115" t="str">
+        <v/>
       </c>
     </row>
     <row r="116">
@@ -5504,20 +6196,26 @@
       <c r="I116">
         <v>60</v>
       </c>
-      <c r="J116" t="str">
-        <v/>
-      </c>
-      <c r="K116" t="str">
-        <v/>
+      <c r="J116">
+        <v>6104.53</v>
+      </c>
+      <c r="K116">
+        <v>11395.47</v>
       </c>
       <c r="L116" t="str">
         <v/>
       </c>
       <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
         <v>PA2404040001</v>
       </c>
-      <c r="N116" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P116" t="str">
+        <v/>
       </c>
     </row>
     <row r="117">
@@ -5548,20 +6246,26 @@
       <c r="I117">
         <v>60</v>
       </c>
-      <c r="J117" t="str">
-        <v/>
-      </c>
-      <c r="K117" t="str">
-        <v/>
+      <c r="J117">
+        <v>2983.74</v>
+      </c>
+      <c r="K117">
+        <v>5692.9</v>
       </c>
       <c r="L117" t="str">
         <v/>
       </c>
       <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
         <v>PA2404130001</v>
       </c>
-      <c r="N117" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P117" t="str">
+        <v/>
       </c>
     </row>
     <row r="118">
@@ -5592,20 +6296,26 @@
       <c r="I118">
         <v>36</v>
       </c>
-      <c r="J118" t="str">
-        <v/>
-      </c>
-      <c r="K118" t="str">
-        <v/>
+      <c r="J118">
+        <v>6810.1</v>
+      </c>
+      <c r="K118">
+        <v>12804.85</v>
       </c>
       <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M118" t="str">
+      <c r="O118" t="str">
         <v>PA2404070001</v>
       </c>
-      <c r="N118" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P118" t="str">
+        <v/>
       </c>
     </row>
     <row r="119">
@@ -5636,20 +6346,26 @@
       <c r="I119">
         <v>36</v>
       </c>
-      <c r="J119" t="str">
-        <v/>
-      </c>
-      <c r="K119" t="str">
-        <v/>
+      <c r="J119">
+        <v>1050.4</v>
+      </c>
+      <c r="K119">
+        <v>2024.36</v>
       </c>
       <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M119" t="str">
+      <c r="O119" t="str">
         <v>PA2404170001</v>
       </c>
-      <c r="N119" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P119" t="str">
+        <v/>
       </c>
     </row>
     <row r="120">
@@ -5680,20 +6396,26 @@
       <c r="I120">
         <v>60</v>
       </c>
-      <c r="J120" t="str">
-        <v/>
-      </c>
-      <c r="K120" t="str">
-        <v/>
+      <c r="J120">
+        <v>1013.35</v>
+      </c>
+      <c r="K120">
+        <v>1986.65</v>
       </c>
       <c r="L120" t="str">
         <v/>
       </c>
       <c r="M120" t="str">
+        <v/>
+      </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
         <v>PA2404240001</v>
       </c>
-      <c r="N120" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P120" t="str">
+        <v/>
       </c>
     </row>
     <row r="121">
@@ -5724,20 +6446,26 @@
       <c r="I121">
         <v>60</v>
       </c>
-      <c r="J121" t="str">
-        <v/>
-      </c>
-      <c r="K121" t="str">
-        <v/>
+      <c r="J121">
+        <v>4127.58</v>
+      </c>
+      <c r="K121">
+        <v>8208.87</v>
       </c>
       <c r="L121" t="str">
         <v/>
       </c>
       <c r="M121" t="str">
+        <v/>
+      </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
         <v>PA2404300001</v>
       </c>
-      <c r="N121" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P121" t="str">
+        <v/>
       </c>
     </row>
     <row r="122">
@@ -5768,20 +6496,26 @@
       <c r="I122">
         <v>36</v>
       </c>
-      <c r="J122" t="str">
-        <v/>
-      </c>
-      <c r="K122" t="str">
-        <v/>
+      <c r="J122">
+        <v>6240.72</v>
+      </c>
+      <c r="K122">
+        <v>12441.52</v>
       </c>
       <c r="L122" t="str">
         <v/>
       </c>
       <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
         <v>PA2405010001</v>
       </c>
-      <c r="N122" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P122" t="str">
+        <v/>
       </c>
     </row>
     <row r="123">
@@ -5812,20 +6546,26 @@
       <c r="I123">
         <v>36</v>
       </c>
-      <c r="J123" t="str">
-        <v/>
-      </c>
-      <c r="K123" t="str">
-        <v/>
+      <c r="J123">
+        <v>6240.72</v>
+      </c>
+      <c r="K123">
+        <v>12441.52</v>
       </c>
       <c r="L123" t="str">
         <v/>
       </c>
       <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
         <v>PA2405010002</v>
       </c>
-      <c r="N123" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P123" t="str">
+        <v/>
       </c>
     </row>
     <row r="124">
@@ -5856,20 +6596,26 @@
       <c r="I124">
         <v>36</v>
       </c>
-      <c r="J124" t="str">
-        <v/>
-      </c>
-      <c r="K124" t="str">
-        <v/>
+      <c r="J124">
+        <v>1026.83</v>
+      </c>
+      <c r="K124">
+        <v>2047.93</v>
       </c>
       <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M124" t="str">
+      <c r="O124" t="str">
         <v>PA2405010003</v>
       </c>
-      <c r="N124" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P124" t="str">
+        <v/>
       </c>
     </row>
     <row r="125">
@@ -5900,20 +6646,26 @@
       <c r="I125">
         <v>36</v>
       </c>
-      <c r="J125" t="str">
-        <v/>
-      </c>
-      <c r="K125" t="str">
-        <v/>
+      <c r="J125">
+        <v>1026.83</v>
+      </c>
+      <c r="K125">
+        <v>2047.94</v>
       </c>
       <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M125" t="str">
+      <c r="O125" t="str">
         <v>PA2405010003</v>
       </c>
-      <c r="N125" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P125" t="str">
+        <v/>
       </c>
     </row>
     <row r="126">
@@ -5944,11 +6696,11 @@
       <c r="I126">
         <v>240</v>
       </c>
-      <c r="J126" t="str">
-        <v/>
-      </c>
-      <c r="K126" t="str">
-        <v/>
+      <c r="J126">
+        <v>97620.1</v>
+      </c>
+      <c r="K126">
+        <v>65110.75</v>
       </c>
       <c r="L126" t="str">
         <v/>
@@ -5957,7 +6709,13 @@
         <v/>
       </c>
       <c r="N126" t="str">
-        <v>บัญชีเดิม:1702100</v>
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v/>
+      </c>
+      <c r="P126" t="str">
+        <v/>
       </c>
     </row>
     <row r="127">
@@ -5988,20 +6746,26 @@
       <c r="I127">
         <v>60</v>
       </c>
-      <c r="J127" t="str">
-        <v/>
-      </c>
-      <c r="K127" t="str">
-        <v/>
+      <c r="J127">
+        <v>79154.42</v>
+      </c>
+      <c r="K127">
+        <v>34845.58</v>
       </c>
       <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127" t="str">
         <v>นายอภิชาติ โตบุญเลี้ยง</v>
       </c>
-      <c r="M127" t="str">
+      <c r="O127" t="str">
         <v>EXP2312020001</v>
       </c>
-      <c r="N127" t="str">
-        <v>บัญชีเดิม:1801000</v>
+      <c r="P127" t="str">
+        <v/>
       </c>
     </row>
     <row r="128">
@@ -6032,20 +6796,26 @@
       <c r="I128">
         <v>60</v>
       </c>
-      <c r="J128" t="str">
-        <v/>
-      </c>
-      <c r="K128" t="str">
-        <v/>
+      <c r="J128">
+        <v>5565.84</v>
+      </c>
+      <c r="K128">
+        <v>12234.16</v>
       </c>
       <c r="L128" t="str">
         <v/>
       </c>
       <c r="M128" t="str">
+        <v/>
+      </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
         <v>PA2406090001</v>
       </c>
-      <c r="N128" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P128" t="str">
+        <v/>
       </c>
     </row>
     <row r="129">
@@ -6076,20 +6846,26 @@
       <c r="I129">
         <v>60</v>
       </c>
-      <c r="J129" t="str">
-        <v/>
-      </c>
-      <c r="K129" t="str">
-        <v/>
+      <c r="J129">
+        <v>15047.12</v>
+      </c>
+      <c r="K129">
+        <v>31681.85</v>
       </c>
       <c r="L129" t="str">
         <v/>
       </c>
       <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
         <v>PA2405230001</v>
       </c>
-      <c r="N129" t="str">
-        <v>บัญชีเดิม:1708000</v>
+      <c r="P129" t="str">
+        <v/>
       </c>
     </row>
     <row r="130">
@@ -6120,20 +6896,26 @@
       <c r="I130">
         <v>60</v>
       </c>
-      <c r="J130" t="str">
-        <v/>
-      </c>
-      <c r="K130" t="str">
-        <v/>
+      <c r="J130">
+        <v>5717.71</v>
+      </c>
+      <c r="K130">
+        <v>12039.3</v>
       </c>
       <c r="L130" t="str">
         <v/>
       </c>
       <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
         <v>PA2405230002</v>
       </c>
-      <c r="N130" t="str">
-        <v>บัญชีเดิม:1708000</v>
+      <c r="P130" t="str">
+        <v/>
       </c>
     </row>
     <row r="131">
@@ -6164,20 +6946,26 @@
       <c r="I131">
         <v>60</v>
       </c>
-      <c r="J131" t="str">
-        <v/>
-      </c>
-      <c r="K131" t="str">
-        <v/>
+      <c r="J131">
+        <v>6303.15</v>
+      </c>
+      <c r="K131">
+        <v>14287.38</v>
       </c>
       <c r="L131" t="str">
         <v/>
       </c>
       <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
         <v>PA2406210001</v>
       </c>
-      <c r="N131" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P131" t="str">
+        <v/>
       </c>
     </row>
     <row r="132">
@@ -6208,20 +6996,26 @@
       <c r="I132">
         <v>60</v>
       </c>
-      <c r="J132" t="str">
-        <v/>
-      </c>
-      <c r="K132" t="str">
-        <v/>
+      <c r="J132">
+        <v>11815.88</v>
+      </c>
+      <c r="K132">
+        <v>26782.25</v>
       </c>
       <c r="L132" t="str">
         <v/>
       </c>
       <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
         <v>PA2406210002</v>
       </c>
-      <c r="N132" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P132" t="str">
+        <v/>
       </c>
     </row>
     <row r="133">
@@ -6252,20 +7046,26 @@
       <c r="I133">
         <v>60</v>
       </c>
-      <c r="J133" t="str">
-        <v/>
-      </c>
-      <c r="K133" t="str">
-        <v/>
+      <c r="J133">
+        <v>4691.83</v>
+      </c>
+      <c r="K133">
+        <v>10635.27</v>
       </c>
       <c r="L133" t="str">
         <v/>
       </c>
       <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
         <v>PA2406210003</v>
       </c>
-      <c r="N133" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P133" t="str">
+        <v/>
       </c>
     </row>
     <row r="134">
@@ -6296,20 +7096,26 @@
       <c r="I134">
         <v>60</v>
       </c>
-      <c r="J134" t="str">
-        <v/>
-      </c>
-      <c r="K134" t="str">
-        <v/>
+      <c r="J134">
+        <v>3442.31</v>
+      </c>
+      <c r="K134">
+        <v>8198.81</v>
       </c>
       <c r="L134" t="str">
         <v/>
       </c>
       <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
         <v>PA2407110001</v>
       </c>
-      <c r="N134" t="str">
-        <v>บัญชีเดิม:1708000</v>
+      <c r="P134" t="str">
+        <v/>
       </c>
     </row>
     <row r="135">
@@ -6340,20 +7146,26 @@
       <c r="I135">
         <v>60</v>
       </c>
-      <c r="J135" t="str">
-        <v/>
-      </c>
-      <c r="K135" t="str">
-        <v/>
+      <c r="J135">
+        <v>3723.69</v>
+      </c>
+      <c r="K135">
+        <v>8776.31</v>
       </c>
       <c r="L135" t="str">
         <v/>
       </c>
       <c r="M135" t="str">
+        <v/>
+      </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
         <v>PA2407060001</v>
       </c>
-      <c r="N135" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P135" t="str">
+        <v/>
       </c>
     </row>
     <row r="136">
@@ -6384,20 +7196,26 @@
       <c r="I136">
         <v>60</v>
       </c>
-      <c r="J136" t="str">
-        <v/>
-      </c>
-      <c r="K136" t="str">
-        <v/>
+      <c r="J136">
+        <v>1358.42</v>
+      </c>
+      <c r="K136">
+        <v>3305.13</v>
       </c>
       <c r="L136" t="str">
         <v/>
       </c>
       <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
         <v>PA2407180001</v>
       </c>
-      <c r="N136" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P136" t="str">
+        <v/>
       </c>
     </row>
     <row r="137">
@@ -6428,20 +7246,26 @@
       <c r="I137">
         <v>60</v>
       </c>
-      <c r="J137" t="str">
-        <v/>
-      </c>
-      <c r="K137" t="str">
-        <v/>
+      <c r="J137">
+        <v>6587.78</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
       </c>
       <c r="L137" t="str">
         <v/>
       </c>
       <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
         <v>PA2407210001</v>
       </c>
-      <c r="N137" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P137" t="str">
+        <v/>
       </c>
     </row>
     <row r="138">
@@ -6472,20 +7296,26 @@
       <c r="I138">
         <v>60</v>
       </c>
-      <c r="J138" t="str">
-        <v/>
-      </c>
-      <c r="K138" t="str">
-        <v/>
+      <c r="J138">
+        <v>706.2</v>
+      </c>
+      <c r="K138">
+        <v>1723.29</v>
       </c>
       <c r="L138" t="str">
         <v/>
       </c>
       <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
         <v>EXP2407190001</v>
       </c>
-      <c r="N138" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P138" t="str">
+        <v/>
       </c>
     </row>
     <row r="139">
@@ -6516,20 +7346,26 @@
       <c r="I139">
         <v>60</v>
       </c>
-      <c r="J139" t="str">
-        <v/>
-      </c>
-      <c r="K139" t="str">
-        <v/>
+      <c r="J139">
+        <v>4114.72</v>
+      </c>
+      <c r="K139">
+        <v>9903.97</v>
       </c>
       <c r="L139" t="str">
         <v/>
       </c>
       <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
         <v>PA2407140002</v>
       </c>
-      <c r="N139" t="str">
-        <v>บัญชีเดิม:1708000</v>
+      <c r="P139" t="str">
+        <v/>
       </c>
     </row>
     <row r="140">
@@ -6560,20 +7396,26 @@
       <c r="I140">
         <v>60</v>
       </c>
-      <c r="J140" t="str">
-        <v/>
-      </c>
-      <c r="K140" t="str">
-        <v/>
+      <c r="J140">
+        <v>1383.61</v>
+      </c>
+      <c r="K140">
+        <v>3366.39</v>
       </c>
       <c r="L140" t="str">
         <v/>
       </c>
       <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
         <v>PA2407180002</v>
       </c>
-      <c r="N140" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P140" t="str">
+        <v/>
       </c>
     </row>
     <row r="141">
@@ -6604,20 +7446,26 @@
       <c r="I141">
         <v>60</v>
       </c>
-      <c r="J141" t="str">
-        <v/>
-      </c>
-      <c r="K141" t="str">
-        <v/>
+      <c r="J141">
+        <v>1383.61</v>
+      </c>
+      <c r="K141">
+        <v>3366.39</v>
       </c>
       <c r="L141" t="str">
         <v/>
       </c>
       <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
         <v>PA2407180002</v>
       </c>
-      <c r="N141" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P141" t="str">
+        <v/>
       </c>
     </row>
     <row r="142">
@@ -6648,20 +7496,26 @@
       <c r="I142">
         <v>60</v>
       </c>
-      <c r="J142" t="str">
-        <v/>
-      </c>
-      <c r="K142" t="str">
-        <v/>
+      <c r="J142">
+        <v>1383.61</v>
+      </c>
+      <c r="K142">
+        <v>3366.39</v>
       </c>
       <c r="L142" t="str">
         <v/>
       </c>
       <c r="M142" t="str">
+        <v/>
+      </c>
+      <c r="N142" t="str">
+        <v/>
+      </c>
+      <c r="O142" t="str">
         <v>PA2407180002</v>
       </c>
-      <c r="N142" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P142" t="str">
+        <v/>
       </c>
     </row>
     <row r="143">
@@ -6692,20 +7546,26 @@
       <c r="I143">
         <v>60</v>
       </c>
-      <c r="J143" t="str">
-        <v/>
-      </c>
-      <c r="K143" t="str">
-        <v/>
+      <c r="J143">
+        <v>1383.61</v>
+      </c>
+      <c r="K143">
+        <v>3366.39</v>
       </c>
       <c r="L143" t="str">
         <v/>
       </c>
       <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
         <v>PA2407180002</v>
       </c>
-      <c r="N143" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P143" t="str">
+        <v/>
       </c>
     </row>
     <row r="144">
@@ -6736,20 +7596,26 @@
       <c r="I144">
         <v>60</v>
       </c>
-      <c r="J144" t="str">
-        <v/>
-      </c>
-      <c r="K144" t="str">
-        <v/>
+      <c r="J144">
+        <v>1383.61</v>
+      </c>
+      <c r="K144">
+        <v>3366.39</v>
       </c>
       <c r="L144" t="str">
         <v/>
       </c>
       <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
         <v>PA2407180002</v>
       </c>
-      <c r="N144" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P144" t="str">
+        <v/>
       </c>
     </row>
     <row r="145">
@@ -6780,20 +7646,26 @@
       <c r="I145">
         <v>60</v>
       </c>
-      <c r="J145" t="str">
-        <v/>
-      </c>
-      <c r="K145" t="str">
-        <v/>
+      <c r="J145">
+        <v>1383.61</v>
+      </c>
+      <c r="K145">
+        <v>3366.39</v>
       </c>
       <c r="L145" t="str">
         <v/>
       </c>
       <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
         <v>PA2407180002</v>
       </c>
-      <c r="N145" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P145" t="str">
+        <v/>
       </c>
     </row>
     <row r="146">
@@ -6824,20 +7696,26 @@
       <c r="I146">
         <v>60</v>
       </c>
-      <c r="J146" t="str">
-        <v/>
-      </c>
-      <c r="K146" t="str">
-        <v/>
+      <c r="J146">
+        <v>2808.15</v>
+      </c>
+      <c r="K146">
+        <v>7091.85</v>
       </c>
       <c r="L146" t="str">
         <v/>
       </c>
       <c r="M146" t="str">
+        <v/>
+      </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
         <v>PA2408010002</v>
       </c>
-      <c r="N146" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P146" t="str">
+        <v/>
       </c>
     </row>
     <row r="147">
@@ -6868,20 +7746,26 @@
       <c r="I147">
         <v>60</v>
       </c>
-      <c r="J147" t="str">
-        <v/>
-      </c>
-      <c r="K147" t="str">
-        <v/>
+      <c r="J147">
+        <v>2749.01</v>
+      </c>
+      <c r="K147">
+        <v>6961.27</v>
       </c>
       <c r="L147" t="str">
         <v/>
       </c>
       <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
         <v>PA2408020001</v>
       </c>
-      <c r="N147" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P147" t="str">
+        <v/>
       </c>
     </row>
     <row r="148">
@@ -6912,20 +7796,26 @@
       <c r="I148">
         <v>36</v>
       </c>
-      <c r="J148" t="str">
-        <v/>
-      </c>
-      <c r="K148" t="str">
-        <v/>
+      <c r="J148">
+        <v>5024.66</v>
+      </c>
+      <c r="K148">
+        <v>12723</v>
       </c>
       <c r="L148" t="str">
         <v/>
       </c>
       <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
         <v>PA2408020002</v>
       </c>
-      <c r="N148" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P148" t="str">
+        <v/>
       </c>
     </row>
     <row r="149">
@@ -6956,20 +7846,26 @@
       <c r="I149">
         <v>36</v>
       </c>
-      <c r="J149" t="str">
-        <v/>
-      </c>
-      <c r="K149" t="str">
-        <v/>
+      <c r="J149">
+        <v>833.24</v>
+      </c>
+      <c r="K149">
+        <v>2110.69</v>
       </c>
       <c r="L149" t="str">
         <v/>
       </c>
       <c r="M149" t="str">
+        <v/>
+      </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
         <v>PA2408020003</v>
       </c>
-      <c r="N149" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P149" t="str">
+        <v/>
       </c>
     </row>
     <row r="150">
@@ -7000,20 +7896,26 @@
       <c r="I150">
         <v>36</v>
       </c>
-      <c r="J150" t="str">
-        <v/>
-      </c>
-      <c r="K150" t="str">
-        <v/>
+      <c r="J150">
+        <v>5798.62</v>
+      </c>
+      <c r="K150">
+        <v>14762.13</v>
       </c>
       <c r="L150" t="str">
         <v/>
       </c>
       <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
         <v>PA2408040004</v>
       </c>
-      <c r="N150" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P150" t="str">
+        <v/>
       </c>
     </row>
     <row r="151">
@@ -7044,20 +7946,26 @@
       <c r="I151">
         <v>60</v>
       </c>
-      <c r="J151" t="str">
-        <v/>
-      </c>
-      <c r="K151" t="str">
-        <v/>
+      <c r="J151">
+        <v>4029.57</v>
+      </c>
+      <c r="K151">
+        <v>10176.04</v>
       </c>
       <c r="L151" t="str">
         <v/>
       </c>
       <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
         <v>PA2408010003</v>
       </c>
-      <c r="N151" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P151" t="str">
+        <v/>
       </c>
     </row>
     <row r="152">
@@ -7088,20 +7996,26 @@
       <c r="I152">
         <v>60</v>
       </c>
-      <c r="J152" t="str">
-        <v/>
-      </c>
-      <c r="K152" t="str">
-        <v/>
+      <c r="J152">
+        <v>5888.07</v>
+      </c>
+      <c r="K152">
+        <v>14868.94</v>
       </c>
       <c r="L152" t="str">
         <v/>
       </c>
       <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
         <v>PA2408010003</v>
       </c>
-      <c r="N152" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P152" t="str">
+        <v/>
       </c>
     </row>
     <row r="153">
@@ -7132,20 +8046,26 @@
       <c r="I153">
         <v>60</v>
       </c>
-      <c r="J153" t="str">
-        <v/>
-      </c>
-      <c r="K153" t="str">
-        <v/>
+      <c r="J153">
+        <v>2054.41</v>
+      </c>
+      <c r="K153">
+        <v>5188.58</v>
       </c>
       <c r="L153" t="str">
         <v/>
       </c>
       <c r="M153" t="str">
+        <v/>
+      </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
         <v>PA2408010003</v>
       </c>
-      <c r="N153" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P153" t="str">
+        <v/>
       </c>
     </row>
     <row r="154">
@@ -7176,20 +8096,26 @@
       <c r="I154">
         <v>60</v>
       </c>
-      <c r="J154" t="str">
-        <v/>
-      </c>
-      <c r="K154" t="str">
-        <v/>
+      <c r="J154">
+        <v>1282.9</v>
+      </c>
+      <c r="K154">
+        <v>3240.46</v>
       </c>
       <c r="L154" t="str">
         <v/>
       </c>
       <c r="M154" t="str">
+        <v/>
+      </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
         <v>PA2408010003</v>
       </c>
-      <c r="N154" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P154" t="str">
+        <v/>
       </c>
     </row>
     <row r="155">
@@ -7220,20 +8146,26 @@
       <c r="I155">
         <v>60</v>
       </c>
-      <c r="J155" t="str">
-        <v/>
-      </c>
-      <c r="K155" t="str">
-        <v/>
+      <c r="J155">
+        <v>2828.39</v>
+      </c>
+      <c r="K155">
+        <v>7162.26</v>
       </c>
       <c r="L155" t="str">
         <v/>
       </c>
       <c r="M155" t="str">
+        <v/>
+      </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
         <v>PA2408020004</v>
       </c>
-      <c r="N155" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P155" t="str">
+        <v/>
       </c>
     </row>
     <row r="156">
@@ -7264,20 +8196,26 @@
       <c r="I156">
         <v>60</v>
       </c>
-      <c r="J156" t="str">
-        <v/>
-      </c>
-      <c r="K156" t="str">
-        <v/>
+      <c r="J156">
+        <v>4495.44</v>
+      </c>
+      <c r="K156">
+        <v>11383.06</v>
       </c>
       <c r="L156" t="str">
         <v/>
       </c>
       <c r="M156" t="str">
+        <v/>
+      </c>
+      <c r="N156" t="str">
+        <v/>
+      </c>
+      <c r="O156" t="str">
         <v>PA2408020005</v>
       </c>
-      <c r="N156" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P156" t="str">
+        <v/>
       </c>
     </row>
     <row r="157">
@@ -7308,20 +8246,26 @@
       <c r="I157">
         <v>60</v>
       </c>
-      <c r="J157" t="str">
-        <v/>
-      </c>
-      <c r="K157" t="str">
-        <v/>
+      <c r="J157">
+        <v>4665.19</v>
+      </c>
+      <c r="K157">
+        <v>11876.87</v>
       </c>
       <c r="L157" t="str">
         <v/>
       </c>
       <c r="M157" t="str">
+        <v/>
+      </c>
+      <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
         <v>PA2408040005</v>
       </c>
-      <c r="N157" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P157" t="str">
+        <v/>
       </c>
     </row>
     <row r="158">
@@ -7352,20 +8296,26 @@
       <c r="I158">
         <v>60</v>
       </c>
-      <c r="J158" t="str">
-        <v/>
-      </c>
-      <c r="K158" t="str">
-        <v/>
+      <c r="J158">
+        <v>1183.22</v>
+      </c>
+      <c r="K158">
+        <v>3013.04</v>
       </c>
       <c r="L158" t="str">
         <v/>
       </c>
       <c r="M158" t="str">
+        <v/>
+      </c>
+      <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
         <v>PA2408040006</v>
       </c>
-      <c r="N158" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P158" t="str">
+        <v/>
       </c>
     </row>
     <row r="159">
@@ -7396,20 +8346,26 @@
       <c r="I159">
         <v>60</v>
       </c>
-      <c r="J159" t="str">
-        <v/>
-      </c>
-      <c r="K159" t="str">
-        <v/>
+      <c r="J159">
+        <v>656.05</v>
+      </c>
+      <c r="K159">
+        <v>1671.05</v>
       </c>
       <c r="L159" t="str">
         <v/>
       </c>
       <c r="M159" t="str">
+        <v/>
+      </c>
+      <c r="N159" t="str">
+        <v/>
+      </c>
+      <c r="O159" t="str">
         <v>PA2408040007</v>
       </c>
-      <c r="N159" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P159" t="str">
+        <v/>
       </c>
     </row>
     <row r="160">
@@ -7440,20 +8396,26 @@
       <c r="I160">
         <v>60</v>
       </c>
-      <c r="J160" t="str">
-        <v/>
-      </c>
-      <c r="K160" t="str">
-        <v/>
+      <c r="J160">
+        <v>1557.78</v>
+      </c>
+      <c r="K160">
+        <v>4053.67</v>
       </c>
       <c r="L160" t="str">
         <v/>
       </c>
       <c r="M160" t="str">
+        <v/>
+      </c>
+      <c r="N160" t="str">
+        <v/>
+      </c>
+      <c r="O160" t="str">
         <v>PA2408120001</v>
       </c>
-      <c r="N160" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P160" t="str">
+        <v/>
       </c>
     </row>
     <row r="161">
@@ -7484,20 +8446,26 @@
       <c r="I161">
         <v>60</v>
       </c>
-      <c r="J161" t="str">
-        <v/>
-      </c>
-      <c r="K161" t="str">
-        <v/>
+      <c r="J161">
+        <v>3150.21</v>
+      </c>
+      <c r="K161">
+        <v>8196.52</v>
       </c>
       <c r="L161" t="str">
         <v/>
       </c>
       <c r="M161" t="str">
+        <v/>
+      </c>
+      <c r="N161" t="str">
+        <v/>
+      </c>
+      <c r="O161" t="str">
         <v>PA2408120002</v>
       </c>
-      <c r="N161" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P161" t="str">
+        <v/>
       </c>
     </row>
     <row r="162">
@@ -7528,20 +8496,26 @@
       <c r="I162">
         <v>36</v>
       </c>
-      <c r="J162" t="str">
-        <v/>
-      </c>
-      <c r="K162" t="str">
-        <v/>
+      <c r="J162">
+        <v>4072.79</v>
+      </c>
+      <c r="K162">
+        <v>10861.79</v>
       </c>
       <c r="L162" t="str">
         <v/>
       </c>
       <c r="M162" t="str">
+        <v/>
+      </c>
+      <c r="N162" t="str">
+        <v/>
+      </c>
+      <c r="O162" t="str">
         <v>PA2408210001</v>
       </c>
-      <c r="N162" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P162" t="str">
+        <v/>
       </c>
     </row>
     <row r="163">
@@ -7572,20 +8546,26 @@
       <c r="I163">
         <v>36</v>
       </c>
-      <c r="J163" t="str">
-        <v/>
-      </c>
-      <c r="K163" t="str">
-        <v/>
+      <c r="J163">
+        <v>764.38</v>
+      </c>
+      <c r="K163">
+        <v>2039.36</v>
       </c>
       <c r="L163" t="str">
         <v/>
       </c>
       <c r="M163" t="str">
+        <v/>
+      </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
         <v>PA2408210001</v>
       </c>
-      <c r="N163" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P163" t="str">
+        <v/>
       </c>
     </row>
     <row r="164">
@@ -7616,20 +8596,26 @@
       <c r="I164">
         <v>60</v>
       </c>
-      <c r="J164" t="str">
-        <v/>
-      </c>
-      <c r="K164" t="str">
-        <v/>
+      <c r="J164">
+        <v>623.47</v>
+      </c>
+      <c r="K164">
+        <v>1618.58</v>
       </c>
       <c r="L164" t="str">
         <v/>
       </c>
       <c r="M164" t="str">
+        <v/>
+      </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
         <v>PA2408110001</v>
       </c>
-      <c r="N164" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P164" t="str">
+        <v/>
       </c>
     </row>
     <row r="165">
@@ -7660,20 +8646,26 @@
       <c r="I165">
         <v>60</v>
       </c>
-      <c r="J165" t="str">
-        <v/>
-      </c>
-      <c r="K165" t="str">
-        <v/>
+      <c r="J165">
+        <v>2432.88</v>
+      </c>
+      <c r="K165">
+        <v>6417.59</v>
       </c>
       <c r="L165" t="str">
+        <v/>
+      </c>
+      <c r="M165" t="str">
+        <v/>
+      </c>
+      <c r="N165" t="str">
         <v>บริษัท อินเด็กซ์ ลิฟวิ่งมอลล์ จำกัด (มหาชน)</v>
       </c>
-      <c r="M165" t="str">
+      <c r="O165" t="str">
         <v>PA2408170001</v>
       </c>
-      <c r="N165" t="str">
-        <v>บัญชีเดิม:1708000</v>
+      <c r="P165" t="str">
+        <v/>
       </c>
     </row>
     <row r="166">
@@ -7704,20 +8696,26 @@
       <c r="I166">
         <v>60</v>
       </c>
-      <c r="J166" t="str">
-        <v/>
-      </c>
-      <c r="K166" t="str">
-        <v/>
+      <c r="J166">
+        <v>1615.83</v>
+      </c>
+      <c r="K166">
+        <v>4262.67</v>
       </c>
       <c r="L166" t="str">
+        <v/>
+      </c>
+      <c r="M166" t="str">
+        <v/>
+      </c>
+      <c r="N166" t="str">
         <v>บริษัท อินเด็กซ์ ลิฟวิ่งมอลล์ จำกัด (มหาชน)</v>
       </c>
-      <c r="M166" t="str">
+      <c r="O166" t="str">
         <v>PA2408170002</v>
       </c>
-      <c r="N166" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P166" t="str">
+        <v/>
       </c>
     </row>
     <row r="167">
@@ -7748,20 +8746,26 @@
       <c r="I167">
         <v>60</v>
       </c>
-      <c r="J167" t="str">
-        <v/>
-      </c>
-      <c r="K167" t="str">
-        <v/>
+      <c r="J167">
+        <v>1615.83</v>
+      </c>
+      <c r="K167">
+        <v>4262.67</v>
       </c>
       <c r="L167" t="str">
+        <v/>
+      </c>
+      <c r="M167" t="str">
+        <v/>
+      </c>
+      <c r="N167" t="str">
         <v>บริษัท อินเด็กซ์ ลิฟวิ่งมอลล์ จำกัด (มหาชน)</v>
       </c>
-      <c r="M167" t="str">
+      <c r="O167" t="str">
         <v>PA2408170002</v>
       </c>
-      <c r="N167" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P167" t="str">
+        <v/>
       </c>
     </row>
     <row r="168">
@@ -7792,20 +8796,26 @@
       <c r="I168">
         <v>60</v>
       </c>
-      <c r="J168" t="str">
-        <v/>
-      </c>
-      <c r="K168" t="str">
-        <v/>
+      <c r="J168">
+        <v>2052.62</v>
+      </c>
+      <c r="K168">
+        <v>5414.68</v>
       </c>
       <c r="L168" t="str">
+        <v/>
+      </c>
+      <c r="M168" t="str">
+        <v/>
+      </c>
+      <c r="N168" t="str">
         <v>บริษัท อินเด็กซ์ ลิฟวิ่งมอลล์ จำกัด (มหาชน)</v>
       </c>
-      <c r="M168" t="str">
+      <c r="O168" t="str">
         <v>PA2408170002</v>
       </c>
-      <c r="N168" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P168" t="str">
+        <v/>
       </c>
     </row>
     <row r="169">
@@ -7836,20 +8846,26 @@
       <c r="I169">
         <v>60</v>
       </c>
-      <c r="J169" t="str">
-        <v/>
-      </c>
-      <c r="K169" t="str">
-        <v/>
+      <c r="J169">
+        <v>372.55</v>
+      </c>
+      <c r="K169">
+        <v>944.27</v>
       </c>
       <c r="L169" t="str">
         <v/>
       </c>
       <c r="M169" t="str">
+        <v/>
+      </c>
+      <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
         <v>PA2408020006</v>
       </c>
-      <c r="N169" t="str">
-        <v>บัญชีเดิม:1708000</v>
+      <c r="P169" t="str">
+        <v/>
       </c>
     </row>
     <row r="170">
@@ -7880,20 +8896,26 @@
       <c r="I170">
         <v>60</v>
       </c>
-      <c r="J170" t="str">
-        <v/>
-      </c>
-      <c r="K170" t="str">
-        <v/>
+      <c r="J170">
+        <v>6629.92</v>
+      </c>
+      <c r="K170">
+        <v>18229.89</v>
       </c>
       <c r="L170" t="str">
         <v/>
       </c>
       <c r="M170" t="str">
+        <v/>
+      </c>
+      <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
         <v>PA2409010001</v>
       </c>
-      <c r="N170" t="str">
-        <v>บัญชีเดิม:1708000</v>
+      <c r="P170" t="str">
+        <v/>
       </c>
     </row>
     <row r="171">
@@ -7924,20 +8946,26 @@
       <c r="I171">
         <v>60</v>
       </c>
-      <c r="J171" t="str">
-        <v/>
-      </c>
-      <c r="K171" t="str">
-        <v/>
+      <c r="J171">
+        <v>554.57</v>
+      </c>
+      <c r="K171">
+        <v>1439.82</v>
       </c>
       <c r="L171" t="str">
         <v/>
       </c>
       <c r="M171" t="str">
+        <v/>
+      </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
         <v>EXP2408110001</v>
       </c>
-      <c r="N171" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P171" t="str">
+        <v/>
       </c>
     </row>
     <row r="172">
@@ -7968,20 +8996,26 @@
       <c r="I172">
         <v>60</v>
       </c>
-      <c r="J172" t="str">
-        <v/>
-      </c>
-      <c r="K172" t="str">
-        <v/>
+      <c r="J172">
+        <v>2337.81</v>
+      </c>
+      <c r="K172">
+        <v>6166.86</v>
       </c>
       <c r="L172" t="str">
         <v/>
       </c>
       <c r="M172" t="str">
+        <v/>
+      </c>
+      <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
         <v>PA2408170003</v>
       </c>
-      <c r="N172" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P172" t="str">
+        <v/>
       </c>
     </row>
     <row r="173">
@@ -8012,20 +9046,26 @@
       <c r="I173">
         <v>36</v>
       </c>
-      <c r="J173" t="str">
-        <v/>
-      </c>
-      <c r="K173" t="str">
-        <v/>
+      <c r="J173">
+        <v>946.79</v>
+      </c>
+      <c r="K173">
+        <v>2417.7</v>
       </c>
       <c r="L173" t="str">
         <v/>
       </c>
       <c r="M173" t="str">
+        <v/>
+      </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
         <v>PA2408050004</v>
       </c>
-      <c r="N173" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P173" t="str">
+        <v/>
       </c>
     </row>
     <row r="174">
@@ -8056,20 +9096,26 @@
       <c r="I174">
         <v>60</v>
       </c>
-      <c r="J174" t="str">
-        <v/>
-      </c>
-      <c r="K174" t="str">
-        <v/>
+      <c r="J174">
+        <v>595.77</v>
+      </c>
+      <c r="K174">
+        <v>1739.74</v>
       </c>
       <c r="L174" t="str">
         <v/>
       </c>
       <c r="M174" t="str">
+        <v/>
+      </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
         <v>PA2409220001</v>
       </c>
-      <c r="N174" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P174" t="str">
+        <v/>
       </c>
     </row>
     <row r="175">
@@ -8100,20 +9146,26 @@
       <c r="I175">
         <v>60</v>
       </c>
-      <c r="J175" t="str">
-        <v/>
-      </c>
-      <c r="K175" t="str">
-        <v/>
+      <c r="J175">
+        <v>7156.36</v>
+      </c>
+      <c r="K175">
+        <v>19843.64</v>
       </c>
       <c r="L175" t="str">
         <v/>
       </c>
       <c r="M175" t="str">
+        <v/>
+      </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
         <v>PA2409040001</v>
       </c>
-      <c r="N175" t="str">
-        <v>บัญชีเดิม:1709000</v>
+      <c r="P175" t="str">
+        <v/>
       </c>
     </row>
     <row r="176">
@@ -8144,20 +9196,26 @@
       <c r="I176">
         <v>60</v>
       </c>
-      <c r="J176" t="str">
-        <v/>
-      </c>
-      <c r="K176" t="str">
-        <v/>
+      <c r="J176">
+        <v>6046.82</v>
+      </c>
+      <c r="K176">
+        <v>15519.59</v>
       </c>
       <c r="L176" t="str">
         <v/>
       </c>
       <c r="M176" t="str">
+        <v/>
+      </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
         <v>PA2408070001</v>
       </c>
-      <c r="N176" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P176" t="str">
+        <v/>
       </c>
     </row>
     <row r="177">
@@ -8188,20 +9246,26 @@
       <c r="I177">
         <v>36</v>
       </c>
-      <c r="J177" t="str">
-        <v/>
-      </c>
-      <c r="K177" t="str">
-        <v/>
+      <c r="J177">
+        <v>4378.74</v>
+      </c>
+      <c r="K177">
+        <v>14303.5</v>
       </c>
       <c r="L177" t="str">
         <v/>
       </c>
       <c r="M177" t="str">
+        <v/>
+      </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
         <v>PA2410300001</v>
       </c>
-      <c r="N177" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P177" t="str">
+        <v/>
       </c>
     </row>
     <row r="178">
@@ -8232,20 +9296,26 @@
       <c r="I178">
         <v>60</v>
       </c>
-      <c r="J178" t="str">
-        <v/>
-      </c>
-      <c r="K178" t="str">
-        <v/>
+      <c r="J178">
+        <v>8248.14</v>
+      </c>
+      <c r="K178">
+        <v>27024.76</v>
       </c>
       <c r="L178" t="str">
         <v/>
       </c>
       <c r="M178" t="str">
+        <v/>
+      </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
         <v>PA2410310001</v>
       </c>
-      <c r="N178" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P178" t="str">
+        <v/>
       </c>
     </row>
     <row r="179">
@@ -8276,20 +9346,26 @@
       <c r="I179">
         <v>36</v>
       </c>
-      <c r="J179" t="str">
-        <v/>
-      </c>
-      <c r="K179" t="str">
-        <v/>
+      <c r="J179">
+        <v>677.26</v>
+      </c>
+      <c r="K179">
+        <v>2219.94</v>
       </c>
       <c r="L179" t="str">
         <v/>
       </c>
       <c r="M179" t="str">
+        <v/>
+      </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
         <v>PA2410310002</v>
       </c>
-      <c r="N179" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P179" t="str">
+        <v/>
       </c>
     </row>
     <row r="180">
@@ -8320,20 +9396,26 @@
       <c r="I180">
         <v>36</v>
       </c>
-      <c r="J180" t="str">
-        <v/>
-      </c>
-      <c r="K180" t="str">
-        <v/>
+      <c r="J180">
+        <v>4347.61</v>
+      </c>
+      <c r="K180">
+        <v>14332.76</v>
       </c>
       <c r="L180" t="str">
+        <v/>
+      </c>
+      <c r="M180" t="str">
+        <v/>
+      </c>
+      <c r="N180" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M180" t="str">
+      <c r="O180" t="str">
         <v>PA2411020001</v>
       </c>
-      <c r="N180" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P180" t="str">
+        <v/>
       </c>
     </row>
     <row r="181">
@@ -8364,20 +9446,26 @@
       <c r="I181">
         <v>36</v>
       </c>
-      <c r="J181" t="str">
-        <v/>
-      </c>
-      <c r="K181" t="str">
-        <v/>
+      <c r="J181">
+        <v>10873.07</v>
+      </c>
+      <c r="K181">
+        <v>35843.75</v>
       </c>
       <c r="L181" t="str">
+        <v/>
+      </c>
+      <c r="M181" t="str">
+        <v/>
+      </c>
+      <c r="N181" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M181" t="str">
+      <c r="O181" t="str">
         <v>PA2411020001</v>
       </c>
-      <c r="N181" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P181" t="str">
+        <v/>
       </c>
     </row>
     <row r="182">
@@ -8408,20 +9496,26 @@
       <c r="I182">
         <v>36</v>
       </c>
-      <c r="J182" t="str">
-        <v/>
-      </c>
-      <c r="K182" t="str">
-        <v/>
+      <c r="J182">
+        <v>624.06</v>
+      </c>
+      <c r="K182">
+        <v>2058.19</v>
       </c>
       <c r="L182" t="str">
         <v/>
       </c>
       <c r="M182" t="str">
+        <v/>
+      </c>
+      <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
         <v>PA2411020002</v>
       </c>
-      <c r="N182" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P182" t="str">
+        <v/>
       </c>
     </row>
     <row r="183">
@@ -8452,20 +9546,26 @@
       <c r="I183">
         <v>36</v>
       </c>
-      <c r="J183" t="str">
-        <v/>
-      </c>
-      <c r="K183" t="str">
-        <v/>
+      <c r="J183">
+        <v>624.06</v>
+      </c>
+      <c r="K183">
+        <v>2058.19</v>
       </c>
       <c r="L183" t="str">
         <v/>
       </c>
       <c r="M183" t="str">
+        <v/>
+      </c>
+      <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
         <v>PA2411020002</v>
       </c>
-      <c r="N183" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P183" t="str">
+        <v/>
       </c>
     </row>
     <row r="184">
@@ -8496,20 +9596,26 @@
       <c r="I184">
         <v>36</v>
       </c>
-      <c r="J184" t="str">
-        <v/>
-      </c>
-      <c r="K184" t="str">
-        <v/>
+      <c r="J184">
+        <v>4327.58</v>
+      </c>
+      <c r="K184">
+        <v>14354.66</v>
       </c>
       <c r="L184" t="str">
+        <v/>
+      </c>
+      <c r="M184" t="str">
+        <v/>
+      </c>
+      <c r="N184" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M184" t="str">
+      <c r="O184" t="str">
         <v>PA2411040001</v>
       </c>
-      <c r="N184" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P184" t="str">
+        <v/>
       </c>
     </row>
     <row r="185">
@@ -8540,20 +9646,26 @@
       <c r="I185">
         <v>36</v>
       </c>
-      <c r="J185" t="str">
-        <v/>
-      </c>
-      <c r="K185" t="str">
-        <v/>
+      <c r="J185">
+        <v>703.52</v>
+      </c>
+      <c r="K185">
+        <v>2651.62</v>
       </c>
       <c r="L185" t="str">
         <v/>
       </c>
       <c r="M185" t="str">
+        <v/>
+      </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
         <v>PA2412140001</v>
       </c>
-      <c r="N185" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P185" t="str">
+        <v/>
       </c>
     </row>
     <row r="186">
@@ -8584,20 +9696,26 @@
       <c r="I186">
         <v>36</v>
       </c>
-      <c r="J186" t="str">
-        <v/>
-      </c>
-      <c r="K186" t="str">
-        <v/>
+      <c r="J186">
+        <v>703.52</v>
+      </c>
+      <c r="K186">
+        <v>2651.62</v>
       </c>
       <c r="L186" t="str">
         <v/>
       </c>
       <c r="M186" t="str">
+        <v/>
+      </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
         <v>PA2412140001</v>
       </c>
-      <c r="N186" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P186" t="str">
+        <v/>
       </c>
     </row>
     <row r="187">
@@ -8628,20 +9746,26 @@
       <c r="I187">
         <v>36</v>
       </c>
-      <c r="J187" t="str">
-        <v/>
-      </c>
-      <c r="K187" t="str">
-        <v/>
+      <c r="J187">
+        <v>3290.74</v>
+      </c>
+      <c r="K187">
+        <v>12197.11</v>
       </c>
       <c r="L187" t="str">
+        <v/>
+      </c>
+      <c r="M187" t="str">
+        <v/>
+      </c>
+      <c r="N187" t="str">
         <v>บริษัท แอดไวซ์ ไอที อินฟินิท จำกัด</v>
       </c>
-      <c r="M187" t="str">
+      <c r="O187" t="str">
         <v>PA2412090001</v>
       </c>
-      <c r="N187" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P187" t="str">
+        <v/>
       </c>
     </row>
     <row r="188">
@@ -8672,20 +9796,26 @@
       <c r="I188">
         <v>36</v>
       </c>
-      <c r="J188" t="str">
-        <v/>
-      </c>
-      <c r="K188" t="str">
-        <v/>
+      <c r="J188">
+        <v>1289.94</v>
+      </c>
+      <c r="K188">
+        <v>4766.13</v>
       </c>
       <c r="L188" t="str">
         <v/>
       </c>
       <c r="M188" t="str">
+        <v/>
+      </c>
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
         <v>PA2412080001</v>
       </c>
-      <c r="N188" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P188" t="str">
+        <v/>
       </c>
     </row>
     <row r="189">
@@ -8716,20 +9846,26 @@
       <c r="I189">
         <v>36</v>
       </c>
-      <c r="J189" t="str">
-        <v/>
-      </c>
-      <c r="K189" t="str">
-        <v/>
+      <c r="J189">
+        <v>635.71</v>
+      </c>
+      <c r="K189">
+        <v>2625.97</v>
       </c>
       <c r="L189" t="str">
+        <v/>
+      </c>
+      <c r="M189" t="str">
+        <v/>
+      </c>
+      <c r="N189" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M189" t="str">
+      <c r="O189" t="str">
         <v>PA2501100001</v>
       </c>
-      <c r="N189" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P189" t="str">
+        <v/>
       </c>
     </row>
     <row r="190">
@@ -8760,20 +9896,26 @@
       <c r="I190">
         <v>36</v>
       </c>
-      <c r="J190" t="str">
-        <v/>
-      </c>
-      <c r="K190" t="str">
-        <v/>
+      <c r="J190">
+        <v>635.71</v>
+      </c>
+      <c r="K190">
+        <v>2625.97</v>
       </c>
       <c r="L190" t="str">
+        <v/>
+      </c>
+      <c r="M190" t="str">
+        <v/>
+      </c>
+      <c r="N190" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M190" t="str">
+      <c r="O190" t="str">
         <v>PA2501100001</v>
       </c>
-      <c r="N190" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P190" t="str">
+        <v/>
       </c>
     </row>
     <row r="191">
@@ -8804,20 +9946,26 @@
       <c r="I191">
         <v>36</v>
       </c>
-      <c r="J191" t="str">
-        <v/>
-      </c>
-      <c r="K191" t="str">
-        <v/>
+      <c r="J191">
+        <v>3626.46</v>
+      </c>
+      <c r="K191">
+        <v>14975.41</v>
       </c>
       <c r="L191" t="str">
+        <v/>
+      </c>
+      <c r="M191" t="str">
+        <v/>
+      </c>
+      <c r="N191" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M191" t="str">
+      <c r="O191" t="str">
         <v>PA2501100001</v>
       </c>
-      <c r="N191" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P191" t="str">
+        <v/>
       </c>
     </row>
     <row r="192">
@@ -8848,20 +9996,26 @@
       <c r="I192">
         <v>36</v>
       </c>
-      <c r="J192" t="str">
-        <v/>
-      </c>
-      <c r="K192" t="str">
-        <v/>
+      <c r="J192">
+        <v>3626.46</v>
+      </c>
+      <c r="K192">
+        <v>14975.41</v>
       </c>
       <c r="L192" t="str">
+        <v/>
+      </c>
+      <c r="M192" t="str">
+        <v/>
+      </c>
+      <c r="N192" t="str">
         <v>บริษัท เพลทตินั่ม อินเตอร์เนชั่นแนล (2002) จำกัด</v>
       </c>
-      <c r="M192" t="str">
+      <c r="O192" t="str">
         <v>PA2501100001</v>
       </c>
-      <c r="N192" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P192" t="str">
+        <v/>
       </c>
     </row>
     <row r="193">
@@ -8892,20 +10046,26 @@
       <c r="I193">
         <v>60</v>
       </c>
-      <c r="J193" t="str">
-        <v/>
-      </c>
-      <c r="K193" t="str">
-        <v/>
+      <c r="J193">
+        <v>8069.29</v>
+      </c>
+      <c r="K193">
+        <v>33910.43</v>
       </c>
       <c r="L193" t="str">
         <v/>
       </c>
       <c r="M193" t="str">
+        <v/>
+      </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
         <v>PA2501150001</v>
       </c>
-      <c r="N193" t="str">
-        <v>บัญชีเดิม:1708000</v>
+      <c r="P193" t="str">
+        <v/>
       </c>
     </row>
     <row r="194">
@@ -8936,20 +10096,26 @@
       <c r="I194">
         <v>60</v>
       </c>
-      <c r="J194" t="str">
-        <v/>
-      </c>
-      <c r="K194" t="str">
-        <v/>
+      <c r="J194">
+        <v>4179.7</v>
+      </c>
+      <c r="K194">
+        <v>17503.48</v>
       </c>
       <c r="L194" t="str">
         <v/>
       </c>
       <c r="M194" t="str">
+        <v/>
+      </c>
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
         <v>PA2501140001</v>
       </c>
-      <c r="N194" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P194" t="str">
+        <v/>
       </c>
     </row>
     <row r="195">
@@ -8980,20 +10146,26 @@
       <c r="I195">
         <v>60</v>
       </c>
-      <c r="J195" t="str">
-        <v/>
-      </c>
-      <c r="K195" t="str">
-        <v/>
+      <c r="J195">
+        <v>2729.67</v>
+      </c>
+      <c r="K195">
+        <v>11512.39</v>
       </c>
       <c r="L195" t="str">
         <v/>
       </c>
       <c r="M195" t="str">
+        <v/>
+      </c>
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
         <v>PA2501160001</v>
       </c>
-      <c r="N195" t="str">
-        <v>บัญชีเดิม:1708000</v>
+      <c r="P195" t="str">
+        <v/>
       </c>
     </row>
     <row r="196">
@@ -9024,20 +10196,26 @@
       <c r="I196">
         <v>60</v>
       </c>
-      <c r="J196" t="str">
-        <v/>
-      </c>
-      <c r="K196" t="str">
-        <v/>
+      <c r="J196">
+        <v>1002.97</v>
+      </c>
+      <c r="K196">
+        <v>4230.67</v>
       </c>
       <c r="L196" t="str">
         <v/>
       </c>
       <c r="M196" t="str">
+        <v/>
+      </c>
+      <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
         <v>PA2501160002</v>
       </c>
-      <c r="N196" t="str">
-        <v>บัญชีเดิม:1707000</v>
+      <c r="P196" t="str">
+        <v/>
       </c>
     </row>
     <row r="197">
@@ -9068,20 +10246,26 @@
       <c r="I197">
         <v>60</v>
       </c>
-      <c r="J197" t="str">
-        <v/>
-      </c>
-      <c r="K197" t="str">
-        <v/>
+      <c r="J197">
+        <v>1704.67</v>
+      </c>
+      <c r="K197">
+        <v>7164.49</v>
       </c>
       <c r="L197" t="str">
         <v/>
       </c>
       <c r="M197" t="str">
+        <v/>
+      </c>
+      <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
         <v>PA2501150003</v>
       </c>
-      <c r="N197" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P197" t="str">
+        <v/>
       </c>
     </row>
     <row r="198">
@@ -9112,20 +10296,26 @@
       <c r="I198">
         <v>60</v>
       </c>
-      <c r="J198" t="str">
-        <v/>
-      </c>
-      <c r="K198" t="str">
-        <v/>
+      <c r="J198">
+        <v>2911.22</v>
+      </c>
+      <c r="K198">
+        <v>12409.34</v>
       </c>
       <c r="L198" t="str">
         <v/>
       </c>
       <c r="M198" t="str">
+        <v/>
+      </c>
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
         <v>PA2501190001</v>
       </c>
-      <c r="N198" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P198" t="str">
+        <v/>
       </c>
     </row>
     <row r="199">
@@ -9156,20 +10346,26 @@
       <c r="I199">
         <v>60</v>
       </c>
-      <c r="J199" t="str">
-        <v/>
-      </c>
-      <c r="K199" t="str">
-        <v/>
+      <c r="J199">
+        <v>1031.72</v>
+      </c>
+      <c r="K199">
+        <v>4398.47</v>
       </c>
       <c r="L199" t="str">
         <v/>
       </c>
       <c r="M199" t="str">
+        <v/>
+      </c>
+      <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
         <v>PA2501190001</v>
       </c>
-      <c r="N199" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P199" t="str">
+        <v/>
       </c>
     </row>
     <row r="200">
@@ -9200,11 +10396,11 @@
       <c r="I200">
         <v>60</v>
       </c>
-      <c r="J200" t="str">
-        <v/>
-      </c>
-      <c r="K200" t="str">
-        <v/>
+      <c r="J200">
+        <v>33403.92</v>
+      </c>
+      <c r="K200">
+        <v>104596.08</v>
       </c>
       <c r="L200" t="str">
         <v/>
@@ -9213,7 +10409,13 @@
         <v/>
       </c>
       <c r="N200" t="str">
-        <v>บัญชีเดิม:1709000</v>
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v/>
       </c>
     </row>
     <row r="201">
@@ -9244,11 +10446,11 @@
       <c r="I201">
         <v>60</v>
       </c>
-      <c r="J201" t="str">
-        <v/>
-      </c>
-      <c r="K201" t="str">
-        <v/>
+      <c r="J201">
+        <v>658494.86</v>
+      </c>
+      <c r="K201">
+        <v>2440505.14</v>
       </c>
       <c r="L201" t="str">
         <v/>
@@ -9257,7 +10459,13 @@
         <v/>
       </c>
       <c r="N201" t="str">
-        <v>บัญชีเดิม:1706000</v>
+        <v/>
+      </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v/>
       </c>
     </row>
     <row r="202">
@@ -9288,20 +10496,26 @@
       <c r="I202">
         <v>60</v>
       </c>
-      <c r="J202" t="str">
-        <v/>
-      </c>
-      <c r="K202" t="str">
-        <v/>
+      <c r="J202">
+        <v>757.57</v>
+      </c>
+      <c r="K202">
+        <v>3634.95</v>
       </c>
       <c r="L202" t="str">
+        <v/>
+      </c>
+      <c r="M202" t="str">
+        <v/>
+      </c>
+      <c r="N202" t="str">
         <v>บริษัท วีนิก กรุ๊ป จำกัด</v>
       </c>
-      <c r="M202" t="str">
+      <c r="O202" t="str">
         <v>PA2502200001</v>
       </c>
-      <c r="N202" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P202" t="str">
+        <v/>
       </c>
     </row>
     <row r="203">
@@ -9332,20 +10546,26 @@
       <c r="I203">
         <v>60</v>
       </c>
-      <c r="J203" t="str">
-        <v/>
-      </c>
-      <c r="K203" t="str">
-        <v/>
+      <c r="J203">
+        <v>3789.57</v>
+      </c>
+      <c r="K203">
+        <v>21637.79</v>
       </c>
       <c r="L203" t="str">
         <v/>
       </c>
       <c r="M203" t="str">
+        <v/>
+      </c>
+      <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
         <v>PA2504030001</v>
       </c>
-      <c r="N203" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P203" t="str">
+        <v/>
       </c>
     </row>
     <row r="204">
@@ -9376,20 +10596,26 @@
       <c r="I204">
         <v>60</v>
       </c>
-      <c r="J204" t="str">
-        <v/>
-      </c>
-      <c r="K204" t="str">
-        <v/>
+      <c r="J204">
+        <v>1941.91</v>
+      </c>
+      <c r="K204">
+        <v>11645.01</v>
       </c>
       <c r="L204" t="str">
         <v/>
       </c>
       <c r="M204" t="str">
+        <v/>
+      </c>
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
         <v>PA2504150001</v>
       </c>
-      <c r="N204" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P204" t="str">
+        <v/>
       </c>
     </row>
     <row r="205">
@@ -9420,20 +10646,26 @@
       <c r="I205">
         <v>60</v>
       </c>
-      <c r="J205" t="str">
-        <v/>
-      </c>
-      <c r="K205" t="str">
-        <v/>
+      <c r="J205">
+        <v>2661.17</v>
+      </c>
+      <c r="K205">
+        <v>17093.04</v>
       </c>
       <c r="L205" t="str">
         <v/>
       </c>
       <c r="M205" t="str">
+        <v/>
+      </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
         <v>PA2504300001</v>
       </c>
-      <c r="N205" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P205" t="str">
+        <v/>
       </c>
     </row>
     <row r="206">
@@ -9464,11 +10696,11 @@
       <c r="I206">
         <v>60</v>
       </c>
-      <c r="J206" t="str">
-        <v/>
-      </c>
-      <c r="K206" t="str">
-        <v/>
+      <c r="J206">
+        <v>23394.01</v>
+      </c>
+      <c r="K206">
+        <v>51549.92</v>
       </c>
       <c r="L206" t="str">
         <v/>
@@ -9477,7 +10709,13 @@
         <v/>
       </c>
       <c r="N206" t="str">
-        <v>บัญชีเดิม:1704000</v>
+        <v/>
+      </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
+      <c r="P206" t="str">
+        <v/>
       </c>
     </row>
     <row r="207">
@@ -9508,20 +10746,26 @@
       <c r="I207">
         <v>60</v>
       </c>
-      <c r="J207" t="str">
-        <v/>
-      </c>
-      <c r="K207" t="str">
-        <v/>
+      <c r="J207">
+        <v>583.46</v>
+      </c>
+      <c r="K207">
+        <v>1790.37</v>
       </c>
       <c r="L207" t="str">
         <v/>
       </c>
       <c r="M207" t="str">
+        <v/>
+      </c>
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
         <v>PA2410090001</v>
       </c>
-      <c r="N207" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P207" t="str">
+        <v/>
       </c>
     </row>
     <row r="208">
@@ -9552,20 +10796,26 @@
       <c r="I208">
         <v>60</v>
       </c>
-      <c r="J208" t="str">
-        <v/>
-      </c>
-      <c r="K208" t="str">
-        <v/>
+      <c r="J208">
+        <v>7734.2</v>
+      </c>
+      <c r="K208">
+        <v>24882.62</v>
       </c>
       <c r="L208" t="str">
         <v/>
       </c>
       <c r="M208" t="str">
+        <v/>
+      </c>
+      <c r="N208" t="str">
+        <v/>
+      </c>
+      <c r="O208" t="str">
         <v>PA2410250001</v>
       </c>
-      <c r="N208" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P208" t="str">
+        <v/>
       </c>
     </row>
     <row r="209">
@@ -9596,20 +10846,26 @@
       <c r="I209">
         <v>240</v>
       </c>
-      <c r="J209" t="str">
-        <v/>
-      </c>
-      <c r="K209" t="str">
-        <v/>
+      <c r="J209">
+        <v>23240.61</v>
+      </c>
+      <c r="K209">
+        <v>42759.39</v>
       </c>
       <c r="L209" t="str">
         <v/>
       </c>
       <c r="M209" t="str">
+        <v/>
+      </c>
+      <c r="N209" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
         <v>EXP2403290001</v>
       </c>
-      <c r="N209" t="str">
-        <v>บัญชีเดิม:1702100</v>
+      <c r="P209" t="str">
+        <v/>
       </c>
     </row>
     <row r="210">
@@ -9640,11 +10896,11 @@
       <c r="I210">
         <v>240</v>
       </c>
-      <c r="J210" t="str">
-        <v/>
-      </c>
-      <c r="K210" t="str">
-        <v/>
+      <c r="J210">
+        <v>118681.78</v>
+      </c>
+      <c r="K210">
+        <v>323590.52</v>
       </c>
       <c r="L210" t="str">
         <v/>
@@ -9653,7 +10909,13 @@
         <v/>
       </c>
       <c r="N210" t="str">
-        <v>บัญชีเดิม:1702100</v>
+        <v/>
+      </c>
+      <c r="O210" t="str">
+        <v/>
+      </c>
+      <c r="P210" t="str">
+        <v/>
       </c>
     </row>
     <row r="211">
@@ -9684,11 +10946,11 @@
       <c r="I211">
         <v>240</v>
       </c>
-      <c r="J211" t="str">
-        <v/>
-      </c>
-      <c r="K211" t="str">
-        <v/>
+      <c r="J211">
+        <v>26108.45</v>
+      </c>
+      <c r="K211">
+        <v>103441.55</v>
       </c>
       <c r="L211" t="str">
         <v/>
@@ -9697,7 +10959,13 @@
         <v/>
       </c>
       <c r="N211" t="str">
-        <v>บัญชีเดิม:1702100</v>
+        <v/>
+      </c>
+      <c r="O211" t="str">
+        <v/>
+      </c>
+      <c r="P211" t="str">
+        <v/>
       </c>
     </row>
     <row r="212">
@@ -9728,20 +10996,26 @@
       <c r="I212">
         <v>60</v>
       </c>
-      <c r="J212" t="str">
-        <v/>
-      </c>
-      <c r="K212" t="str">
-        <v/>
+      <c r="J212">
+        <v>232.1</v>
+      </c>
+      <c r="K212">
+        <v>1627.71</v>
       </c>
       <c r="L212" t="str">
         <v/>
       </c>
       <c r="M212" t="str">
+        <v/>
+      </c>
+      <c r="N212" t="str">
+        <v/>
+      </c>
+      <c r="O212" t="str">
         <v>PA2505180001</v>
       </c>
-      <c r="N212" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P212" t="str">
+        <v/>
       </c>
     </row>
     <row r="213">
@@ -9772,20 +11046,26 @@
       <c r="I213">
         <v>60</v>
       </c>
-      <c r="J213" t="str">
-        <v/>
-      </c>
-      <c r="K213" t="str">
-        <v/>
+      <c r="J213">
+        <v>2588.54</v>
+      </c>
+      <c r="K213">
+        <v>16944.16</v>
       </c>
       <c r="L213" t="str">
+        <v/>
+      </c>
+      <c r="M213" t="str">
+        <v/>
+      </c>
+      <c r="N213" t="str">
         <v>บริษัท เซ็นทรัลเทรดดิ้ง จำกัด</v>
       </c>
-      <c r="M213" t="str">
+      <c r="O213" t="str">
         <v>PA2505040001</v>
       </c>
-      <c r="N213" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P213" t="str">
+        <v/>
       </c>
     </row>
     <row r="214">
@@ -9816,20 +11096,26 @@
       <c r="I214">
         <v>60</v>
       </c>
-      <c r="J214" t="str">
-        <v/>
-      </c>
-      <c r="K214" t="str">
-        <v/>
+      <c r="J214">
+        <v>1473.8</v>
+      </c>
+      <c r="K214">
+        <v>9647.7</v>
       </c>
       <c r="L214" t="str">
+        <v/>
+      </c>
+      <c r="M214" t="str">
+        <v/>
+      </c>
+      <c r="N214" t="str">
         <v>บริษัท เซ็นทรัลเทรดดิ้ง จำกัด</v>
       </c>
-      <c r="M214" t="str">
+      <c r="O214" t="str">
         <v>PA2505040001</v>
       </c>
-      <c r="N214" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P214" t="str">
+        <v/>
       </c>
     </row>
     <row r="215">
@@ -9860,20 +11146,26 @@
       <c r="I215">
         <v>60</v>
       </c>
-      <c r="J215" t="str">
-        <v/>
-      </c>
-      <c r="K215" t="str">
-        <v/>
+      <c r="J215">
+        <v>1473.8</v>
+      </c>
+      <c r="K215">
+        <v>9647.7</v>
       </c>
       <c r="L215" t="str">
+        <v/>
+      </c>
+      <c r="M215" t="str">
+        <v/>
+      </c>
+      <c r="N215" t="str">
         <v>บริษัท เซ็นทรัลเทรดดิ้ง จำกัด</v>
       </c>
-      <c r="M215" t="str">
+      <c r="O215" t="str">
         <v>PA2505040001</v>
       </c>
-      <c r="N215" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P215" t="str">
+        <v/>
       </c>
     </row>
     <row r="216">
@@ -9904,20 +11196,26 @@
       <c r="I216">
         <v>60</v>
       </c>
-      <c r="J216" t="str">
-        <v/>
-      </c>
-      <c r="K216" t="str">
-        <v/>
+      <c r="J216">
+        <v>5077.2</v>
+      </c>
+      <c r="K216">
+        <v>42959.88</v>
       </c>
       <c r="L216" t="str">
+        <v/>
+      </c>
+      <c r="M216" t="str">
+        <v/>
+      </c>
+      <c r="N216" t="str">
         <v>บริษัท แอปเปิ้ล เซาท์ เอเชีย (ประเทศไทย) จำกัด</v>
       </c>
-      <c r="M216" t="str">
+      <c r="O216" t="str">
         <v>PA2506220001</v>
       </c>
-      <c r="N216" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P216" t="str">
+        <v/>
       </c>
     </row>
     <row r="217">
@@ -9948,20 +11246,26 @@
       <c r="I217">
         <v>60</v>
       </c>
-      <c r="J217" t="str">
-        <v/>
-      </c>
-      <c r="K217" t="str">
-        <v/>
+      <c r="J217">
+        <v>321.3</v>
+      </c>
+      <c r="K217">
+        <v>2719.59</v>
       </c>
       <c r="L217" t="str">
         <v/>
       </c>
       <c r="M217" t="str">
+        <v/>
+      </c>
+      <c r="N217" t="str">
+        <v/>
+      </c>
+      <c r="O217" t="str">
         <v>PA2506220002</v>
       </c>
-      <c r="N217" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P217" t="str">
+        <v/>
       </c>
     </row>
     <row r="218">
@@ -9992,20 +11296,26 @@
       <c r="I218">
         <v>60</v>
       </c>
-      <c r="J218" t="str">
-        <v/>
-      </c>
-      <c r="K218" t="str">
-        <v/>
+      <c r="J218">
+        <v>3765.03</v>
+      </c>
+      <c r="K218">
+        <v>32419.88</v>
       </c>
       <c r="L218" t="str">
         <v/>
       </c>
       <c r="M218" t="str">
+        <v/>
+      </c>
+      <c r="N218" t="str">
+        <v/>
+      </c>
+      <c r="O218" t="str">
         <v>PA2506250003</v>
       </c>
-      <c r="N218" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P218" t="str">
+        <v/>
       </c>
     </row>
     <row r="219">
@@ -10036,20 +11346,26 @@
       <c r="I219">
         <v>60</v>
       </c>
-      <c r="J219" t="str">
-        <v/>
-      </c>
-      <c r="K219" t="str">
-        <v/>
+      <c r="J219">
+        <v>385.2</v>
+      </c>
+      <c r="K219">
+        <v>3317.74</v>
       </c>
       <c r="L219" t="str">
         <v/>
       </c>
       <c r="M219" t="str">
+        <v/>
+      </c>
+      <c r="N219" t="str">
+        <v/>
+      </c>
+      <c r="O219" t="str">
         <v>PA2506250003</v>
       </c>
-      <c r="N219" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P219" t="str">
+        <v/>
       </c>
     </row>
     <row r="220">
@@ -10080,20 +11396,26 @@
       <c r="I220">
         <v>60</v>
       </c>
-      <c r="J220" t="str">
-        <v/>
-      </c>
-      <c r="K220" t="str">
-        <v/>
+      <c r="J220">
+        <v>1554.85</v>
+      </c>
+      <c r="K220">
+        <v>13389.08</v>
       </c>
       <c r="L220" t="str">
         <v/>
       </c>
       <c r="M220" t="str">
+        <v/>
+      </c>
+      <c r="N220" t="str">
+        <v/>
+      </c>
+      <c r="O220" t="str">
         <v>PA2506250002</v>
       </c>
-      <c r="N220" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P220" t="str">
+        <v/>
       </c>
     </row>
     <row r="221">
@@ -10124,20 +11446,26 @@
       <c r="I221">
         <v>60</v>
       </c>
-      <c r="J221" t="str">
-        <v/>
-      </c>
-      <c r="K221" t="str">
-        <v/>
+      <c r="J221">
+        <v>917.79</v>
+      </c>
+      <c r="K221">
+        <v>8241.09</v>
       </c>
       <c r="L221" t="str">
+        <v/>
+      </c>
+      <c r="M221" t="str">
+        <v/>
+      </c>
+      <c r="N221" t="str">
         <v>บริษัท เอส.เอ็ม.ที.อิเล็คโทรมาร์ท จำกัด</v>
       </c>
-      <c r="M221" t="str">
+      <c r="O221" t="str">
         <v>PA2507020001</v>
       </c>
-      <c r="N221" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P221" t="str">
+        <v/>
       </c>
     </row>
     <row r="222">
@@ -10168,20 +11496,26 @@
       <c r="I222">
         <v>36</v>
       </c>
-      <c r="J222" t="str">
-        <v/>
-      </c>
-      <c r="K222" t="str">
-        <v/>
+      <c r="J222">
+        <v>566.38</v>
+      </c>
+      <c r="K222">
+        <v>4657.92</v>
       </c>
       <c r="L222" t="str">
         <v/>
       </c>
       <c r="M222" t="str">
+        <v/>
+      </c>
+      <c r="N222" t="str">
+        <v/>
+      </c>
+      <c r="O222" t="str">
         <v>PA2506170001</v>
       </c>
-      <c r="N222" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P222" t="str">
+        <v/>
       </c>
     </row>
     <row r="223">
@@ -10212,20 +11546,26 @@
       <c r="I223">
         <v>36</v>
       </c>
-      <c r="J223" t="str">
-        <v/>
-      </c>
-      <c r="K223" t="str">
-        <v/>
+      <c r="J223">
+        <v>4481.65</v>
+      </c>
+      <c r="K223">
+        <v>49714.61</v>
       </c>
       <c r="L223" t="str">
         <v/>
       </c>
       <c r="M223" t="str">
+        <v/>
+      </c>
+      <c r="N223" t="str">
+        <v/>
+      </c>
+      <c r="O223" t="str">
         <v>PA2508030001</v>
       </c>
-      <c r="N223" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P223" t="str">
+        <v/>
       </c>
     </row>
     <row r="224">
@@ -10256,20 +11596,26 @@
       <c r="I224">
         <v>36</v>
       </c>
-      <c r="J224" t="str">
-        <v/>
-      </c>
-      <c r="K224" t="str">
-        <v/>
+      <c r="J224">
+        <v>319.04</v>
+      </c>
+      <c r="K224">
+        <v>2900.59</v>
       </c>
       <c r="L224" t="str">
+        <v/>
+      </c>
+      <c r="M224" t="str">
+        <v/>
+      </c>
+      <c r="N224" t="str">
         <v>บริษัท ทีเอเจ แอสโซซิเอชั่น จำกัด</v>
       </c>
-      <c r="M224" t="str">
+      <c r="O224" t="str">
         <v>PA2507040001</v>
       </c>
-      <c r="N224" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P224" t="str">
+        <v/>
       </c>
     </row>
     <row r="225">
@@ -10300,20 +11646,26 @@
       <c r="I225">
         <v>60</v>
       </c>
-      <c r="J225" t="str">
-        <v/>
-      </c>
-      <c r="K225" t="str">
-        <v/>
+      <c r="J225">
+        <v>1285.1</v>
+      </c>
+      <c r="K225">
+        <v>16098.08</v>
       </c>
       <c r="L225" t="str">
         <v/>
       </c>
       <c r="M225" t="str">
+        <v/>
+      </c>
+      <c r="N225" t="str">
+        <v/>
+      </c>
+      <c r="O225" t="str">
         <v>PA2508190002</v>
       </c>
-      <c r="N225" t="str">
-        <v>บัญชีเดิม:1708000</v>
+      <c r="P225" t="str">
+        <v/>
       </c>
     </row>
     <row r="226">
@@ -10344,20 +11696,26 @@
       <c r="I226">
         <v>60</v>
       </c>
-      <c r="J226" t="str">
-        <v/>
-      </c>
-      <c r="K226" t="str">
-        <v/>
+      <c r="J226">
+        <v>536.73</v>
+      </c>
+      <c r="K226">
+        <v>8061.4</v>
       </c>
       <c r="L226" t="str">
+        <v/>
+      </c>
+      <c r="M226" t="str">
+        <v/>
+      </c>
+      <c r="N226" t="str">
         <v>บริษัท แอปเปิ้ล เซาท์ เอเชีย (ประเทศไทย) จำกัด</v>
       </c>
-      <c r="M226" t="str">
+      <c r="O226" t="str">
         <v>PA2509090001</v>
       </c>
-      <c r="N226" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P226" t="str">
+        <v/>
       </c>
     </row>
     <row r="227">
@@ -10388,20 +11746,26 @@
       <c r="I227">
         <v>60</v>
       </c>
-      <c r="J227" t="str">
-        <v/>
-      </c>
-      <c r="K227" t="str">
-        <v/>
+      <c r="J227">
+        <v>1172.72</v>
+      </c>
+      <c r="K227">
+        <v>17612.33</v>
       </c>
       <c r="L227" t="str">
+        <v/>
+      </c>
+      <c r="M227" t="str">
+        <v/>
+      </c>
+      <c r="N227" t="str">
         <v>บริษัท แอปเปิ้ล เซาท์ เอเชีย (ประเทศไทย) จำกัด</v>
       </c>
-      <c r="M227" t="str">
+      <c r="O227" t="str">
         <v>PA2509090002</v>
       </c>
-      <c r="N227" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P227" t="str">
+        <v/>
       </c>
     </row>
     <row r="228">
@@ -10432,11 +11796,11 @@
       <c r="I228">
         <v>60</v>
       </c>
-      <c r="J228" t="str">
-        <v/>
-      </c>
-      <c r="K228" t="str">
-        <v/>
+      <c r="J228">
+        <v>220.06</v>
+      </c>
+      <c r="K228">
+        <v>3368.72</v>
       </c>
       <c r="L228" t="str">
         <v/>
@@ -10445,7 +11809,13 @@
         <v/>
       </c>
       <c r="N228" t="str">
-        <v>บัญชีเดิม:1704000</v>
+        <v/>
+      </c>
+      <c r="O228" t="str">
+        <v/>
+      </c>
+      <c r="P228" t="str">
+        <v/>
       </c>
     </row>
     <row r="229">
@@ -10476,20 +11846,26 @@
       <c r="I229">
         <v>60</v>
       </c>
-      <c r="J229" t="str">
-        <v/>
-      </c>
-      <c r="K229" t="str">
-        <v/>
+      <c r="J229">
+        <v>1257.23</v>
+      </c>
+      <c r="K229">
+        <v>25752.12</v>
       </c>
       <c r="L229" t="str">
+        <v/>
+      </c>
+      <c r="M229" t="str">
+        <v/>
+      </c>
+      <c r="N229" t="str">
         <v>บริษัท โฮมเอ็กซ์เพิร์ท เอเชีย จำกัด</v>
       </c>
-      <c r="M229" t="str">
+      <c r="O229" t="str">
         <v>EXP2510080001</v>
       </c>
-      <c r="N229" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P229" t="str">
+        <v/>
       </c>
     </row>
     <row r="230">
@@ -10520,20 +11896,26 @@
       <c r="I230">
         <v>60</v>
       </c>
-      <c r="J230" t="str">
-        <v/>
-      </c>
-      <c r="K230" t="str">
-        <v/>
+      <c r="J230">
+        <v>224.84</v>
+      </c>
+      <c r="K230">
+        <v>4495.16</v>
       </c>
       <c r="L230" t="str">
         <v/>
       </c>
       <c r="M230" t="str">
+        <v/>
+      </c>
+      <c r="N230" t="str">
+        <v/>
+      </c>
+      <c r="O230" t="str">
         <v>PA2510060001</v>
       </c>
-      <c r="N230" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P230" t="str">
+        <v/>
       </c>
     </row>
     <row r="231">
@@ -10564,20 +11946,26 @@
       <c r="I231">
         <v>60</v>
       </c>
-      <c r="J231" t="str">
-        <v/>
-      </c>
-      <c r="K231" t="str">
-        <v/>
+      <c r="J231">
+        <v>224.84</v>
+      </c>
+      <c r="K231">
+        <v>4495.16</v>
       </c>
       <c r="L231" t="str">
         <v/>
       </c>
       <c r="M231" t="str">
+        <v/>
+      </c>
+      <c r="N231" t="str">
+        <v/>
+      </c>
+      <c r="O231" t="str">
         <v>PA2510060001</v>
       </c>
-      <c r="N231" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P231" t="str">
+        <v/>
       </c>
     </row>
     <row r="232">
@@ -10608,20 +11996,26 @@
       <c r="I232">
         <v>36</v>
       </c>
-      <c r="J232" t="str">
-        <v/>
-      </c>
-      <c r="K232" t="str">
-        <v/>
+      <c r="J232">
+        <v>1794.04</v>
+      </c>
+      <c r="K232">
+        <v>37205.96</v>
       </c>
       <c r="L232" t="str">
+        <v/>
+      </c>
+      <c r="M232" t="str">
+        <v/>
+      </c>
+      <c r="N232" t="str">
         <v>บริษัท อะไหล่เซิร์ฟเวอร์ จำกัด</v>
       </c>
-      <c r="M232" t="str">
+      <c r="O232" t="str">
         <v>PA2510090001</v>
       </c>
-      <c r="N232" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P232" t="str">
+        <v/>
       </c>
     </row>
     <row r="233">
@@ -10652,20 +12046,26 @@
       <c r="I233">
         <v>60</v>
       </c>
-      <c r="J233" t="str">
-        <v/>
-      </c>
-      <c r="K233" t="str">
-        <v/>
+      <c r="J233">
+        <v>1169.47</v>
+      </c>
+      <c r="K233">
+        <v>26209.04</v>
       </c>
       <c r="L233" t="str">
+        <v/>
+      </c>
+      <c r="M233" t="str">
+        <v/>
+      </c>
+      <c r="N233" t="str">
         <v>บริษัท ทีจี เซลลูล่าร์เวิลด์ จำกัด</v>
       </c>
-      <c r="M233" t="str">
+      <c r="O233" t="str">
         <v>PA2510150001</v>
       </c>
-      <c r="N233" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P233" t="str">
+        <v/>
       </c>
     </row>
     <row r="234">
@@ -10696,20 +12096,26 @@
       <c r="I234">
         <v>36</v>
       </c>
-      <c r="J234" t="str">
-        <v/>
-      </c>
-      <c r="K234" t="str">
-        <v/>
+      <c r="J234">
+        <v>39.27</v>
+      </c>
+      <c r="K234">
+        <v>1082.23</v>
       </c>
       <c r="L234" t="str">
         <v/>
       </c>
       <c r="M234" t="str">
+        <v/>
+      </c>
+      <c r="N234" t="str">
+        <v/>
+      </c>
+      <c r="O234" t="str">
         <v>PA2510290001</v>
       </c>
-      <c r="N234" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P234" t="str">
+        <v/>
       </c>
     </row>
     <row r="235">
@@ -10740,20 +12146,26 @@
       <c r="I235">
         <v>60</v>
       </c>
-      <c r="J235" t="str">
-        <v/>
-      </c>
-      <c r="K235" t="str">
-        <v/>
+      <c r="J235">
+        <v>2118.61</v>
+      </c>
+      <c r="K235">
+        <v>58329.05</v>
       </c>
       <c r="L235" t="str">
         <v/>
       </c>
       <c r="M235" t="str">
+        <v/>
+      </c>
+      <c r="N235" t="str">
+        <v/>
+      </c>
+      <c r="O235" t="str">
         <v>PA2510290002</v>
       </c>
-      <c r="N235" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P235" t="str">
+        <v/>
       </c>
     </row>
     <row r="236">
@@ -10784,20 +12196,26 @@
       <c r="I236">
         <v>60</v>
       </c>
-      <c r="J236" t="str">
-        <v/>
-      </c>
-      <c r="K236" t="str">
-        <v/>
+      <c r="J236">
+        <v>188.77</v>
+      </c>
+      <c r="K236">
+        <v>5755.16</v>
       </c>
       <c r="L236" t="str">
+        <v/>
+      </c>
+      <c r="M236" t="str">
+        <v/>
+      </c>
+      <c r="N236" t="str">
         <v>บริษัท เวอแดนซี่ เทคโนโลยี จำกัด</v>
       </c>
-      <c r="M236" t="str">
+      <c r="O236" t="str">
         <v>PA2511040001</v>
       </c>
-      <c r="N236" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P236" t="str">
+        <v/>
       </c>
     </row>
     <row r="237">
@@ -10828,20 +12246,26 @@
       <c r="I237">
         <v>60</v>
       </c>
-      <c r="J237" t="str">
-        <v/>
-      </c>
-      <c r="K237" t="str">
-        <v/>
+      <c r="J237">
+        <v>774.16</v>
+      </c>
+      <c r="K237">
+        <v>23599.67</v>
       </c>
       <c r="L237" t="str">
         <v/>
       </c>
       <c r="M237" t="str">
+        <v/>
+      </c>
+      <c r="N237" t="str">
+        <v/>
+      </c>
+      <c r="O237" t="str">
         <v>PA2511040002</v>
       </c>
-      <c r="N237" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P237" t="str">
+        <v/>
       </c>
     </row>
     <row r="238">
@@ -10872,20 +12296,26 @@
       <c r="I238">
         <v>60</v>
       </c>
-      <c r="J238" t="str">
-        <v/>
-      </c>
-      <c r="K238" t="str">
-        <v/>
+      <c r="J238">
+        <v>1056.45</v>
+      </c>
+      <c r="K238">
+        <v>32204.53</v>
       </c>
       <c r="L238" t="str">
         <v/>
       </c>
       <c r="M238" t="str">
+        <v/>
+      </c>
+      <c r="N238" t="str">
+        <v/>
+      </c>
+      <c r="O238" t="str">
         <v>PA2511040003</v>
       </c>
-      <c r="N238" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P238" t="str">
+        <v/>
       </c>
     </row>
     <row r="239">
@@ -10916,20 +12346,26 @@
       <c r="I239">
         <v>60</v>
       </c>
-      <c r="J239" t="str">
-        <v/>
-      </c>
-      <c r="K239" t="str">
-        <v/>
+      <c r="J239">
+        <v>1173.88</v>
+      </c>
+      <c r="K239">
+        <v>44433.59</v>
       </c>
       <c r="L239" t="str">
+        <v/>
+      </c>
+      <c r="M239" t="str">
+        <v/>
+      </c>
+      <c r="N239" t="str">
         <v>บริษัท แอปเปิ้ล เซาท์ เอเชีย (ประเทศไทย) จำกัด</v>
       </c>
-      <c r="M239" t="str">
+      <c r="O239" t="str">
         <v>PA2511150001</v>
       </c>
-      <c r="N239" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P239" t="str">
+        <v/>
       </c>
     </row>
     <row r="240">
@@ -10960,20 +12396,26 @@
       <c r="I240">
         <v>36</v>
       </c>
-      <c r="J240" t="str">
-        <v/>
-      </c>
-      <c r="K240" t="str">
-        <v/>
+      <c r="J240">
+        <v>301.29</v>
+      </c>
+      <c r="K240">
+        <v>17446.37</v>
       </c>
       <c r="L240" t="str">
         <v/>
       </c>
       <c r="M240" t="str">
+        <v/>
+      </c>
+      <c r="N240" t="str">
+        <v/>
+      </c>
+      <c r="O240" t="str">
         <v>PA2512010001</v>
       </c>
-      <c r="N240" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P240" t="str">
+        <v/>
       </c>
     </row>
     <row r="241">
@@ -11004,20 +12446,26 @@
       <c r="I241">
         <v>36</v>
       </c>
-      <c r="J241" t="str">
-        <v/>
-      </c>
-      <c r="K241" t="str">
-        <v/>
+      <c r="J241">
+        <v>325.62</v>
+      </c>
+      <c r="K241">
+        <v>17693.07</v>
       </c>
       <c r="L241" t="str">
         <v/>
       </c>
       <c r="M241" t="str">
+        <v/>
+      </c>
+      <c r="N241" t="str">
+        <v/>
+      </c>
+      <c r="O241" t="str">
         <v>PA2511290001</v>
       </c>
-      <c r="N241" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P241" t="str">
+        <v/>
       </c>
     </row>
     <row r="242">
@@ -11048,20 +12496,26 @@
       <c r="I242">
         <v>36</v>
       </c>
-      <c r="J242" t="str">
-        <v/>
-      </c>
-      <c r="K242" t="str">
-        <v/>
+      <c r="J242">
+        <v>63.99</v>
+      </c>
+      <c r="K242">
+        <v>3094.89</v>
       </c>
       <c r="L242" t="str">
         <v/>
       </c>
       <c r="M242" t="str">
+        <v/>
+      </c>
+      <c r="N242" t="str">
+        <v/>
+      </c>
+      <c r="O242" t="str">
         <v>PA2511250001</v>
       </c>
-      <c r="N242" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P242" t="str">
+        <v/>
       </c>
     </row>
     <row r="243">
@@ -11092,20 +12546,26 @@
       <c r="I243">
         <v>60</v>
       </c>
-      <c r="J243" t="str">
-        <v/>
-      </c>
-      <c r="K243" t="str">
-        <v/>
+      <c r="J243">
+        <v>933.47</v>
+      </c>
+      <c r="K243">
+        <v>27010.46</v>
       </c>
       <c r="L243" t="str">
+        <v/>
+      </c>
+      <c r="M243" t="str">
+        <v/>
+      </c>
+      <c r="N243" t="str">
         <v>บริษัท เซ็นทรัลเทรดดิ้ง จำกัด</v>
       </c>
-      <c r="M243" t="str">
+      <c r="O243" t="str">
         <v>PA2511010001</v>
       </c>
-      <c r="N243" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P243" t="str">
+        <v/>
       </c>
     </row>
     <row r="244">
@@ -11136,20 +12596,26 @@
       <c r="I244">
         <v>60</v>
       </c>
-      <c r="J244" t="str">
-        <v/>
-      </c>
-      <c r="K244" t="str">
-        <v/>
+      <c r="J244">
+        <v>466.72</v>
+      </c>
+      <c r="K244">
+        <v>13505.24</v>
       </c>
       <c r="L244" t="str">
+        <v/>
+      </c>
+      <c r="M244" t="str">
+        <v/>
+      </c>
+      <c r="N244" t="str">
         <v>บริษัท เซ็นทรัลเทรดดิ้ง จำกัด</v>
       </c>
-      <c r="M244" t="str">
+      <c r="O244" t="str">
         <v>PA2511010001</v>
       </c>
-      <c r="N244" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P244" t="str">
+        <v/>
       </c>
     </row>
     <row r="245">
@@ -11180,20 +12646,26 @@
       <c r="I245">
         <v>60</v>
       </c>
-      <c r="J245" t="str">
-        <v/>
-      </c>
-      <c r="K245" t="str">
-        <v/>
+      <c r="J245">
+        <v>303.93</v>
+      </c>
+      <c r="K245">
+        <v>20251.88</v>
       </c>
       <c r="L245" t="str">
         <v/>
       </c>
       <c r="M245" t="str">
+        <v/>
+      </c>
+      <c r="N245" t="str">
+        <v/>
+      </c>
+      <c r="O245" t="str">
         <v>PA2512050001</v>
       </c>
-      <c r="N245" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P245" t="str">
+        <v/>
       </c>
     </row>
     <row r="246">
@@ -11224,20 +12696,26 @@
       <c r="I246">
         <v>60</v>
       </c>
-      <c r="J246" t="str">
-        <v/>
-      </c>
-      <c r="K246" t="str">
-        <v/>
+      <c r="J246">
+        <v>474.54</v>
+      </c>
+      <c r="K246">
+        <v>22329.2</v>
       </c>
       <c r="L246" t="str">
+        <v/>
+      </c>
+      <c r="M246" t="str">
+        <v/>
+      </c>
+      <c r="N246" t="str">
         <v>บริษัท โฮมเอ็กซ์เพิร์ท เอเชีย จำกัด</v>
       </c>
-      <c r="M246" t="str">
+      <c r="O246" t="str">
         <v>PA2511240003</v>
       </c>
-      <c r="N246" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P246" t="str">
+        <v/>
       </c>
     </row>
     <row r="247">
@@ -11268,20 +12746,26 @@
       <c r="I247">
         <v>60</v>
       </c>
-      <c r="J247" t="str">
-        <v/>
-      </c>
-      <c r="K247" t="str">
-        <v/>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>38224.3</v>
       </c>
       <c r="L247" t="str">
+        <v/>
+      </c>
+      <c r="M247" t="str">
+        <v/>
+      </c>
+      <c r="N247" t="str">
         <v>บริษัท เพาเวอร์ฟูล คอมมูนิเคชั่น จำกัด</v>
       </c>
-      <c r="M247" t="str">
+      <c r="O247" t="str">
         <v>PA2603080001</v>
       </c>
-      <c r="N247" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P247" t="str">
+        <v>ไม่พบข้อมูลค่าเสื่อม - คำนวณใหม่</v>
       </c>
     </row>
     <row r="248">
@@ -11312,20 +12796,26 @@
       <c r="I248">
         <v>60</v>
       </c>
-      <c r="J248" t="str">
-        <v/>
-      </c>
-      <c r="K248" t="str">
-        <v/>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>38224.3</v>
       </c>
       <c r="L248" t="str">
+        <v/>
+      </c>
+      <c r="M248" t="str">
+        <v/>
+      </c>
+      <c r="N248" t="str">
         <v>บริษัท เพาเวอร์ฟูล คอมมูนิเคชั่น จำกัด</v>
       </c>
-      <c r="M248" t="str">
+      <c r="O248" t="str">
         <v>PA2603080001</v>
       </c>
-      <c r="N248" t="str">
-        <v>บัญชีเดิม:1704000</v>
+      <c r="P248" t="str">
+        <v>ไม่พบข้อมูลค่าเสื่อม - คำนวณใหม่</v>
       </c>
     </row>
     <row r="249">
@@ -11356,44 +12846,47 @@
       <c r="I249">
         <v>36</v>
       </c>
-      <c r="J249" t="str">
-        <v/>
-      </c>
-      <c r="K249" t="str">
-        <v/>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>38747.66</v>
       </c>
       <c r="L249" t="str">
+        <v/>
+      </c>
+      <c r="M249" t="str">
+        <v/>
+      </c>
+      <c r="N249" t="str">
         <v>บริษัท แอดไวซ์ ไอที อินฟินิท จำกัด</v>
       </c>
-      <c r="M249" t="str">
+      <c r="O249" t="str">
         <v>PA2603050001</v>
       </c>
-      <c r="N249" t="str">
-        <v>บัญชีเดิม:1705000</v>
+      <c r="P249" t="str">
+        <v>ไม่พบข้อมูลค่าเสื่อม - คำนวณใหม่</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N249"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P249"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>หมวดหมู่เดิม</v>
       </c>
       <c r="B1" t="str">
-        <v>บัญชีเดิม</v>
+        <v>หมวดหมู่ E-Tax</v>
       </c>
       <c r="C1" t="str">
-        <v>หมวดหมู่ E-Tax</v>
-      </c>
-      <c r="D1" t="str">
         <v>อายุใช้งาน(เดือน)</v>
       </c>
     </row>
@@ -11402,12 +12895,9 @@
         <v>computer</v>
       </c>
       <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
         <v>อุปกรณ์คอมพิวเตอร์</v>
       </c>
-      <c r="D2">
+      <c r="C2">
         <v>36</v>
       </c>
     </row>
@@ -11416,12 +12906,9 @@
         <v>เครื่องใช้สำนักงาน</v>
       </c>
       <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v>อุปกรณ์สำนักงาน</v>
-      </c>
-      <c r="D3">
+        <v>อุปกรณ์สำนักงาน</v>
+      </c>
+      <c r="C3">
         <v>60</v>
       </c>
     </row>
@@ -11430,12 +12917,9 @@
         <v>software</v>
       </c>
       <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
         <v>สินทรัพย์ไม่มีตัวตน</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <v>60</v>
       </c>
     </row>
@@ -11444,12 +12928,9 @@
         <v>ยานพาหนะ</v>
       </c>
       <c r="B5" t="str">
-        <v/>
-      </c>
-      <c r="C5" t="str">
         <v>ยานพาหนะ</v>
       </c>
-      <c r="D5">
+      <c r="C5">
         <v>60</v>
       </c>
     </row>
@@ -11458,12 +12939,9 @@
         <v>เครื่องตกแต่งสำนักงาน</v>
       </c>
       <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
         <v>เครื่องตกแต่งและติดตั้ง</v>
       </c>
-      <c r="D6">
+      <c r="C6">
         <v>60</v>
       </c>
     </row>
@@ -11472,12 +12950,9 @@
         <v>อาคาร-ส่วนปรับปรุงเพิ่ม</v>
       </c>
       <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
         <v>ส่วนต่อเติมอาคาร</v>
       </c>
-      <c r="D7">
+      <c r="C7">
         <v>240</v>
       </c>
     </row>
@@ -11486,12 +12961,9 @@
         <v>ชุดเฟอร์นิเจอร์</v>
       </c>
       <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v>อุปกรณ์สำนักงาน</v>
-      </c>
-      <c r="D8">
+        <v>อุปกรณ์สำนักงาน</v>
+      </c>
+      <c r="C8">
         <v>60</v>
       </c>
     </row>
@@ -11500,18 +12972,15 @@
         <v>ป้ายบริษัท</v>
       </c>
       <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
         <v>เครื่องตกแต่งและติดตั้ง</v>
       </c>
-      <c r="D9">
+      <c r="C9">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C9"/>
   </ignoredErrors>
 </worksheet>
 </file>